--- a/psychopy_exp_files/sequences/learning_block2_fixed-middle-10_27.xlsx
+++ b/psychopy_exp_files/sequences/learning_block2_fixed-middle-10_27.xlsx
@@ -564,27 +564,27 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>stimuli/guitar/guitar_10.jpg</t>
+          <t>stimuli/phone/phone_04.jpg</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_07.jpg</t>
+          <t>stimuli/lamp/lamp_08.jpg</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_02.jpg</t>
+          <t>stimuli/hammer/hammer_26.jpg</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_25.jpg</t>
+          <t>stimuli/key/key_10.jpg</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>guitar</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -599,40 +599,40 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>key</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P2" t="n">
         <v>0.47</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.31</v>
+        <v>0.25</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S2" t="n">
         <v>2</v>
       </c>
       <c r="T2" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="U2" t="n">
         <v>14</v>
@@ -641,7 +641,7 @@
         <v>7</v>
       </c>
       <c r="W2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3">
@@ -663,22 +663,22 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_07.jpg</t>
+          <t>stimuli/lamp/lamp_08.jpg</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_28.jpg</t>
+          <t>stimuli/bicycle/bicycle_35.jpg</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_35.jpg</t>
+          <t>stimuli/house/house_05.jpg</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>stimuli/key/key_14.jpg</t>
+          <t>stimuli/bread/bread_49.jpg</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -688,22 +688,22 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>house</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -713,18 +713,18 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.8</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.31</v>
+        <v>0.36</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S3" t="n">
@@ -734,13 +734,13 @@
         <v>14</v>
       </c>
       <c r="U3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V3" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="W3" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -762,42 +762,42 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_28.jpg</t>
+          <t>stimuli/bicycle/bicycle_35.jpg</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_19.jpg</t>
+          <t>stimuli/house/house_05.jpg</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_02.jpg</t>
+          <t>stimuli/ball/ball_23.jpg</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>stimuli/pencil/pencil_25.jpg</t>
+          <t>stimuli/key/key_10.jpg</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>house</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
           <t>ball</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>bicycle</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>hammer</t>
-        </is>
-      </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>pencil</t>
+          <t>key</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -816,10 +816,10 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>0.58</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.31</v>
+        <v>0.36</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
@@ -830,16 +830,16 @@
         <v>4</v>
       </c>
       <c r="T4" t="n">
+        <v>2</v>
+      </c>
+      <c r="U4" t="n">
+        <v>9</v>
+      </c>
+      <c r="V4" t="n">
         <v>1</v>
       </c>
-      <c r="U4" t="n">
-        <v>2</v>
-      </c>
-      <c r="V4" t="n">
-        <v>7</v>
-      </c>
       <c r="W4" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5">
@@ -861,44 +861,44 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_19.jpg</t>
+          <t>stimuli/house/house_05.jpg</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>stimuli/dog/dog_30.jpg</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>stimuli/jacket/jacket_35.jpg</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
           <t>stimuli/bread/bread_49.jpg</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>stimuli/chair/chair_35.jpg</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>stimuli/hand/hand_42.jpg</t>
-        </is>
-      </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>house</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
+          <t>dog</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>jacket</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
           <t>bread</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>chair</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>hand</t>
-        </is>
-      </c>
       <c r="M5" t="inlineStr">
         <is>
           <t>left</t>
@@ -915,10 +915,10 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>0.8</v>
+        <v>0.58</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.58</v>
+        <v>0.47</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
@@ -929,16 +929,16 @@
         <v>5</v>
       </c>
       <c r="T5" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="U5" t="n">
+        <v>5</v>
+      </c>
+      <c r="V5" t="n">
+        <v>10</v>
+      </c>
+      <c r="W5" t="n">
         <v>3</v>
-      </c>
-      <c r="V5" t="n">
-        <v>4</v>
-      </c>
-      <c r="W5" t="n">
-        <v>8</v>
       </c>
     </row>
     <row r="6">
@@ -960,27 +960,27 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_49.jpg</t>
+          <t>stimuli/dog/dog_30.jpg</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_35.jpg</t>
+          <t>stimuli/chair/chair_16.jpg</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_06.jpg</t>
+          <t>stimuli/flower/flower_22.jpg</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>stimuli/key/key_14.jpg</t>
+          <t>stimuli/hand/hand_30.jpg</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -995,17 +995,17 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -1017,18 +1017,18 @@
         <v>0.75</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.47</v>
+        <v>0.58</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S6" t="n">
         <v>6</v>
       </c>
       <c r="T6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="U6" t="n">
         <v>4</v>
@@ -1037,7 +1037,7 @@
         <v>6</v>
       </c>
       <c r="W6" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7">
@@ -1059,22 +1059,22 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_35.jpg</t>
+          <t>stimuli/chair/chair_16.jpg</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_18.jpg</t>
+          <t>stimuli/ball/ball_23.jpg</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>stimuli/house/house_25.jpg</t>
+          <t>stimuli/hammer/hammer_26.jpg</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>stimuli/pencil/pencil_25.jpg</t>
+          <t>stimuli/glasses/glasses_02.jpg</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1084,17 +1084,17 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>pencil</t>
+          <t>glasses</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1113,7 +1113,7 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>0.64</v>
+        <v>0.75</v>
       </c>
       <c r="Q7" t="n">
         <v>0.47</v>
@@ -1130,13 +1130,13 @@
         <v>4</v>
       </c>
       <c r="U7" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="V7" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="W7" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8">
@@ -1158,84 +1158,84 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_18.jpg</t>
+          <t>stimuli/ball/ball_23.jpg</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_06.jpg</t>
+          <t>stimuli/flower/flower_22.jpg</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>stimuli/key/key_14.jpg</t>
+          <t>stimuli/lamp/lamp_08.jpg</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_07.jpg</t>
+          <t>stimuli/dog/dog_30.jpg</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
+          <t>ball</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>flower</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>lamp</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
           <t>dog</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>flower</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>key</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>lamp</t>
-        </is>
-      </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>0.58</v>
+        <v>0.4</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S8" t="n">
         <v>8</v>
       </c>
       <c r="T8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="U8" t="n">
         <v>6</v>
       </c>
       <c r="V8" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="W8" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9">
@@ -1257,22 +1257,22 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_06.jpg</t>
+          <t>stimuli/flower/flower_22.jpg</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_02.jpg</t>
+          <t>stimuli/hammer/hammer_26.jpg</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_19.jpg</t>
+          <t>stimuli/bread/bread_49.jpg</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_35.jpg</t>
+          <t>stimuli/bicycle/bicycle_35.jpg</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1287,14 +1287,14 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
+          <t>bread</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
           <t>bicycle</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>chair</t>
-        </is>
-      </c>
       <c r="M9" t="inlineStr">
         <is>
           <t>left</t>
@@ -1311,10 +1311,10 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>0.33</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
@@ -1331,10 +1331,10 @@
         <v>7</v>
       </c>
       <c r="V9" t="n">
+        <v>3</v>
+      </c>
+      <c r="W9" t="n">
         <v>2</v>
-      </c>
-      <c r="W9" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="10">
@@ -1356,22 +1356,22 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_02.jpg</t>
+          <t>stimuli/hammer/hammer_26.jpg</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_42.jpg</t>
+          <t>stimuli/jacket/jacket_35.jpg</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>stimuli/key/key_14.jpg</t>
+          <t>stimuli/bicycle/bicycle_35.jpg</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_18.jpg</t>
+          <t>stimuli/chair/chair_16.jpg</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1381,22 +1381,22 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1406,18 +1406,18 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.47</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S10" t="n">
@@ -1427,13 +1427,13 @@
         <v>7</v>
       </c>
       <c r="U10" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="V10" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="W10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11">
@@ -1455,84 +1455,84 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_42.jpg</t>
+          <t>stimuli/jacket/jacket_35.jpg</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>stimuli/house/house_25.jpg</t>
+          <t>stimuli/hand/hand_30.jpg</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>stimuli/guitar/guitar_10.jpg</t>
+          <t>stimuli/phone/phone_04.jpg</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_06.jpg</t>
+          <t>stimuli/dog/dog_30.jpg</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
+          <t>jacket</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
           <t>hand</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>house</t>
-        </is>
-      </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>guitar</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P11" t="n">
         <v>0.67</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S11" t="n">
         <v>11</v>
       </c>
       <c r="T11" t="n">
+        <v>10</v>
+      </c>
+      <c r="U11" t="n">
         <v>8</v>
       </c>
-      <c r="U11" t="n">
-        <v>9</v>
-      </c>
       <c r="V11" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="W11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12">
@@ -1554,44 +1554,44 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>stimuli/house/house_25.jpg</t>
+          <t>stimuli/hand/hand_30.jpg</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_25.jpg</t>
+          <t>stimuli/bread/bread_49.jpg</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_28.jpg</t>
+          <t>stimuli/house/house_05.jpg</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_18.jpg</t>
+          <t>stimuli/ball/ball_23.jpg</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
+          <t>hand</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>bread</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
           <t>house</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>jacket</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>ball</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>dog</t>
-        </is>
-      </c>
       <c r="M12" t="inlineStr">
         <is>
           <t>center</t>
@@ -1599,16 +1599,16 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>0.6</v>
+        <v>0.53</v>
       </c>
       <c r="Q12" t="n">
         <v>0.33</v>
@@ -1622,16 +1622,16 @@
         <v>12</v>
       </c>
       <c r="T12" t="n">
+        <v>8</v>
+      </c>
+      <c r="U12" t="n">
+        <v>3</v>
+      </c>
+      <c r="V12" t="n">
         <v>9</v>
       </c>
-      <c r="U12" t="n">
-        <v>10</v>
-      </c>
-      <c r="V12" t="n">
+      <c r="W12" t="n">
         <v>1</v>
-      </c>
-      <c r="W12" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="13">
@@ -1653,27 +1653,27 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_25.jpg</t>
+          <t>stimuli/bread/bread_49.jpg</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>stimuli/key/key_14.jpg</t>
+          <t>stimuli/key/key_10.jpg</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_07.jpg</t>
+          <t>stimuli/lamp/lamp_08.jpg</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_49.jpg</t>
+          <t>stimuli/house/house_05.jpg</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>house</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1703,25 +1703,25 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P13" t="n">
         <v>0.73</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.53</v>
+        <v>0.6</v>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S13" t="n">
         <v>13</v>
       </c>
       <c r="T13" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="U13" t="n">
         <v>15</v>
@@ -1730,7 +1730,7 @@
         <v>14</v>
       </c>
       <c r="W13" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14">
@@ -1752,22 +1752,22 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>stimuli/key/key_14.jpg</t>
+          <t>stimuli/key/key_10.jpg</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>stimuli/pencil/pencil_25.jpg</t>
+          <t>stimuli/glasses/glasses_02.jpg</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_28.jpg</t>
+          <t>stimuli/bicycle/bicycle_35.jpg</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_02.jpg</t>
+          <t>stimuli/hand/hand_30.jpg</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1777,17 +1777,17 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>pencil</t>
+          <t>glasses</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1809,7 +1809,7 @@
         <v>0.73</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.33</v>
+        <v>0.2</v>
       </c>
       <c r="R14" t="inlineStr">
         <is>
@@ -1823,13 +1823,13 @@
         <v>15</v>
       </c>
       <c r="U14" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="V14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15">
@@ -1851,42 +1851,42 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>stimuli/pencil/pencil_23.jpg</t>
+          <t>stimuli/lamp/lamp_30.jpg</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>stimuli/guitar/guitar_26.jpg</t>
+          <t>stimuli/car/car_04.jpg</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_30.jpg</t>
+          <t>stimuli/ball/ball_04.jpg</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_44.jpg</t>
+          <t>stimuli/phone/phone_22.jpg</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>pencil</t>
+          <t>lamp</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>guitar</t>
+          <t>car</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1905,10 +1905,10 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>0.75</v>
+        <v>0.42</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.36</v>
+        <v>0.25</v>
       </c>
       <c r="R15" t="inlineStr">
         <is>
@@ -1919,16 +1919,16 @@
         <v>2</v>
       </c>
       <c r="T15" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="U15" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="V15" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="W15" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
     </row>
     <row r="16">
@@ -1950,47 +1950,47 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>stimuli/guitar/guitar_26.jpg</t>
+          <t>stimuli/car/car_04.jpg</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_01.jpg</t>
+          <t>stimuli/dog/dog_11.jpg</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_03.jpg</t>
+          <t>stimuli/hand/hand_20.jpg</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_22.jpg</t>
+          <t>stimuli/pencil/pencil_15.jpg</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>guitar</t>
+          <t>car</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>pencil</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -2000,34 +2000,34 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.53</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.36</v>
+        <v>0.25</v>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S16" t="n">
         <v>3</v>
       </c>
       <c r="T16" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="U16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="V16" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="W16" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
     </row>
     <row r="17">
@@ -2049,42 +2049,42 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_01.jpg</t>
+          <t>stimuli/dog/dog_11.jpg</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_30.jpg</t>
+          <t>stimuli/bread/bread_25.jpg</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_04.jpg</t>
+          <t>stimuli/jacket/jacket_06.jpg</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>stimuli/key/key_13.jpg</t>
+          <t>stimuli/lamp/lamp_30.jpg</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
+          <t>dog</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
           <t>bread</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="K17" t="inlineStr">
         <is>
           <t>jacket</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>ball</t>
-        </is>
-      </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>lamp</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -2094,19 +2094,19 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0.64</v>
+        <v>0.8</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.31</v>
+        <v>0.2</v>
       </c>
       <c r="R17" t="inlineStr">
         <is>
@@ -2117,16 +2117,16 @@
         <v>4</v>
       </c>
       <c r="T17" t="n">
+        <v>5</v>
+      </c>
+      <c r="U17" t="n">
         <v>3</v>
       </c>
-      <c r="U17" t="n">
+      <c r="V17" t="n">
         <v>10</v>
       </c>
-      <c r="V17" t="n">
-        <v>1</v>
-      </c>
       <c r="W17" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="18">
@@ -2148,47 +2148,47 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_30.jpg</t>
+          <t>stimuli/bread/bread_25.jpg</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_10.jpg</t>
+          <t>stimuli/jacket/jacket_06.jpg</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_44.jpg</t>
+          <t>stimuli/flower/flower_21.jpg</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_41.jpg</t>
+          <t>stimuli/ball/ball_04.jpg</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
+          <t>bread</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
           <t>jacket</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>hand</t>
-        </is>
-      </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>lamp</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -2198,34 +2198,34 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0.53</v>
+        <v>0.8</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.42</v>
+        <v>0.58</v>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S18" t="n">
         <v>5</v>
       </c>
       <c r="T18" t="n">
+        <v>3</v>
+      </c>
+      <c r="U18" t="n">
         <v>10</v>
       </c>
-      <c r="U18" t="n">
-        <v>8</v>
-      </c>
       <c r="V18" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="W18" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -2247,27 +2247,27 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_10.jpg</t>
+          <t>stimuli/jacket/jacket_06.jpg</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_03.jpg</t>
+          <t>stimuli/flower/flower_21.jpg</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>stimuli/pencil/pencil_23.jpg</t>
+          <t>stimuli/lamp/lamp_30.jpg</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_01.jpg</t>
+          <t>stimuli/dog/dog_11.jpg</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2277,22 +2277,22 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>pencil</t>
+          <t>lamp</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -2308,23 +2308,23 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S19" t="n">
         <v>6</v>
       </c>
       <c r="T19" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U19" t="n">
         <v>6</v>
       </c>
       <c r="V19" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="W19" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -2346,22 +2346,22 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_03.jpg</t>
+          <t>stimuli/flower/flower_21.jpg</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_13.jpg</t>
+          <t>stimuli/chair/chair_04.jpg</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_39.jpg</t>
+          <t>stimuli/bicycle/bicycle_28.jpg</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>stimuli/key/key_13.jpg</t>
+          <t>stimuli/house/house_10.jpg</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2376,38 +2376,38 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>house</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.8</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.47</v>
+        <v>0.64</v>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S20" t="n">
@@ -2420,10 +2420,10 @@
         <v>4</v>
       </c>
       <c r="V20" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="W20" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="21">
@@ -2445,22 +2445,22 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_13.jpg</t>
+          <t>stimuli/chair/chair_04.jpg</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
+          <t>stimuli/bicycle/bicycle_28.jpg</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
           <t>stimuli/ball/ball_04.jpg</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>stimuli/house/house_15.jpg</t>
-        </is>
-      </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_44.jpg</t>
+          <t>stimuli/hammer/hammer_09.jpg</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2470,17 +2470,17 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
           <t>ball</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>house</t>
-        </is>
-      </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2490,19 +2490,19 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P21" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="R21" t="inlineStr">
         <is>
@@ -2516,13 +2516,13 @@
         <v>4</v>
       </c>
       <c r="U21" t="n">
+        <v>2</v>
+      </c>
+      <c r="V21" t="n">
         <v>1</v>
       </c>
-      <c r="V21" t="n">
-        <v>9</v>
-      </c>
       <c r="W21" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="22">
@@ -2544,52 +2544,52 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_04.jpg</t>
+          <t>stimuli/bicycle/bicycle_28.jpg</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>stimuli/house/house_15.jpg</t>
+          <t>stimuli/hand/hand_20.jpg</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>stimuli/pencil/pencil_23.jpg</t>
+          <t>stimuli/house/house_10.jpg</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_10.jpg</t>
+          <t>stimuli/bread/bread_25.jpg</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
+          <t>hand</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
           <t>house</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>pencil</t>
-        </is>
-      </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -2598,30 +2598,30 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>0.53</v>
+        <v>0.75</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.27</v>
+        <v>0.33</v>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S22" t="n">
         <v>9</v>
       </c>
       <c r="T22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U22" t="n">
+        <v>8</v>
+      </c>
+      <c r="V22" t="n">
         <v>9</v>
       </c>
-      <c r="V22" t="n">
-        <v>16</v>
-      </c>
       <c r="W22" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23">
@@ -2643,37 +2643,37 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>stimuli/house/house_15.jpg</t>
+          <t>stimuli/hand/hand_20.jpg</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_39.jpg</t>
+          <t>stimuli/ball/ball_04.jpg</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_10.jpg</t>
+          <t>stimuli/lamp/lamp_30.jpg</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_13.jpg</t>
+          <t>stimuli/chair/chair_04.jpg</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>lamp</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -2683,7 +2683,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -2693,31 +2693,31 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P23" t="n">
-        <v>0.33</v>
+        <v>0.6</v>
       </c>
       <c r="Q23" t="n">
         <v>0.2</v>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S23" t="n">
         <v>10</v>
       </c>
       <c r="T23" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U23" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="V23" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="W23" t="n">
         <v>4</v>
@@ -2742,84 +2742,84 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_39.jpg</t>
+          <t>stimuli/ball/ball_04.jpg</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_44.jpg</t>
+          <t>stimuli/house/house_10.jpg</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_22.jpg</t>
+          <t>stimuli/car/car_04.jpg</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>stimuli/guitar/guitar_26.jpg</t>
+          <t>stimuli/flower/flower_21.jpg</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>house</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>car</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>guitar</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P24" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.6</v>
+        <v>0.33</v>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S24" t="n">
         <v>11</v>
       </c>
       <c r="T24" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="U24" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="V24" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="W24" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="25">
@@ -2841,84 +2841,84 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_44.jpg</t>
+          <t>stimuli/house/house_10.jpg</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_22.jpg</t>
+          <t>stimuli/hammer/hammer_09.jpg</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>stimuli/pencil/pencil_23.jpg</t>
+          <t>stimuli/bread/bread_25.jpg</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_10.jpg</t>
+          <t>stimuli/bicycle/bicycle_28.jpg</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
+          <t>house</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>hammer</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>bread</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
           <t>bicycle</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>hammer</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>pencil</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>hand</t>
-        </is>
-      </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P25" t="n">
-        <v>0.73</v>
+        <v>0.53</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.47</v>
+        <v>0.27</v>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S25" t="n">
         <v>12</v>
       </c>
       <c r="T25" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="U25" t="n">
         <v>7</v>
       </c>
       <c r="V25" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="W25" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26">
@@ -2940,22 +2940,22 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_22.jpg</t>
+          <t>stimuli/hammer/hammer_09.jpg</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_41.jpg</t>
+          <t>stimuli/phone/phone_22.jpg</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>stimuli/guitar/guitar_26.jpg</t>
+          <t>stimuli/lamp/lamp_30.jpg</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_30.jpg</t>
+          <t>stimuli/flower/flower_21.jpg</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2965,43 +2965,43 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
+          <t>phone</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
           <t>lamp</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>guitar</t>
-        </is>
-      </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P26" t="n">
-        <v>0.73</v>
+        <v>0.8</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.6</v>
+        <v>0.47</v>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S26" t="n">
@@ -3011,13 +3011,13 @@
         <v>7</v>
       </c>
       <c r="U26" t="n">
+        <v>17</v>
+      </c>
+      <c r="V26" t="n">
         <v>14</v>
       </c>
-      <c r="V26" t="n">
-        <v>13</v>
-      </c>
       <c r="W26" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="27">
@@ -3039,47 +3039,47 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_41.jpg</t>
+          <t>stimuli/phone/phone_22.jpg</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>stimuli/key/key_13.jpg</t>
+          <t>stimuli/pencil/pencil_15.jpg</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_03.jpg</t>
+          <t>stimuli/bicycle/bicycle_28.jpg</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>stimuli/pencil/pencil_23.jpg</t>
+          <t>stimuli/lamp/lamp_30.jpg</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
+          <t>phone</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>pencil</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
           <t>lamp</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>key</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>flower</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>pencil</t>
-        </is>
-      </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -3089,34 +3089,34 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P27" t="n">
-        <v>0.53</v>
+        <v>0.4</v>
       </c>
       <c r="Q27" t="n">
         <v>0.26</v>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S27" t="n">
         <v>14</v>
       </c>
       <c r="T27" t="n">
+        <v>17</v>
+      </c>
+      <c r="U27" t="n">
+        <v>16</v>
+      </c>
+      <c r="V27" t="n">
+        <v>2</v>
+      </c>
+      <c r="W27" t="n">
         <v>14</v>
-      </c>
-      <c r="U27" t="n">
-        <v>15</v>
-      </c>
-      <c r="V27" t="n">
-        <v>6</v>
-      </c>
-      <c r="W27" t="n">
-        <v>16</v>
       </c>
     </row>
     <row r="28">
@@ -3138,27 +3138,27 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>stimuli/guitar/guitar_10.jpg</t>
+          <t>stimuli/phone/phone_04.jpg</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_07.jpg</t>
+          <t>stimuli/lamp/lamp_08.jpg</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_19.jpg</t>
+          <t>stimuli/ball/ball_23.jpg</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_25.jpg</t>
+          <t>stimuli/key/key_10.jpg</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>guitar</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>key</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -3183,19 +3183,19 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P28" t="n">
-        <v>0.75</v>
+        <v>0.58</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.31</v>
+        <v>0.25</v>
       </c>
       <c r="R28" t="inlineStr">
         <is>
@@ -3206,16 +3206,16 @@
         <v>2</v>
       </c>
       <c r="T28" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="U28" t="n">
         <v>14</v>
       </c>
       <c r="V28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W28" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="29">
@@ -3237,22 +3237,22 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_07.jpg</t>
+          <t>stimuli/lamp/lamp_08.jpg</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_28.jpg</t>
+          <t>stimuli/bicycle/bicycle_35.jpg</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_42.jpg</t>
+          <t>stimuli/bread/bread_49.jpg</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>stimuli/pencil/pencil_25.jpg</t>
+          <t>stimuli/glasses/glasses_02.jpg</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3262,27 +3262,27 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>pencil</t>
+          <t>glasses</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
@@ -3291,14 +3291,14 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>0.47</v>
+        <v>0.36</v>
       </c>
       <c r="Q29" t="n">
         <v>0.25</v>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S29" t="n">
@@ -3308,13 +3308,13 @@
         <v>14</v>
       </c>
       <c r="U29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V29" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="W29" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="30">
@@ -3336,37 +3336,37 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_28.jpg</t>
+          <t>stimuli/bicycle/bicycle_35.jpg</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_19.jpg</t>
+          <t>stimuli/house/house_05.jpg</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_49.jpg</t>
+          <t>stimuli/flower/flower_22.jpg</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_42.jpg</t>
+          <t>stimuli/hand/hand_30.jpg</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>house</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -3386,31 +3386,31 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P30" t="n">
-        <v>0.8</v>
+        <v>0.64</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.53</v>
+        <v>0.47</v>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S30" t="n">
         <v>4</v>
       </c>
       <c r="T30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U30" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="V30" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="W30" t="n">
         <v>8</v>
@@ -3435,84 +3435,84 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_19.jpg</t>
+          <t>stimuli/house/house_05.jpg</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_49.jpg</t>
+          <t>stimuli/dog/dog_30.jpg</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_35.jpg</t>
+          <t>stimuli/jacket/jacket_35.jpg</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>stimuli/guitar/guitar_10.jpg</t>
+          <t>stimuli/key/key_10.jpg</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>house</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>guitar</t>
+          <t>key</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P31" t="n">
-        <v>0.8</v>
+        <v>0.58</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.27</v>
+        <v>0.42</v>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S31" t="n">
         <v>5</v>
       </c>
       <c r="T31" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="U31" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="V31" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="W31" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="32">
@@ -3534,27 +3534,27 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_49.jpg</t>
+          <t>stimuli/dog/dog_30.jpg</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_35.jpg</t>
+          <t>stimuli/chair/chair_16.jpg</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>stimuli/house/house_25.jpg</t>
+          <t>stimuli/hammer/hammer_26.jpg</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>stimuli/key/key_14.jpg</t>
+          <t>stimuli/hand/hand_30.jpg</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -3579,19 +3579,19 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P32" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="Q32" t="n">
         <v>0.58</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>0.47</v>
       </c>
       <c r="R32" t="inlineStr">
         <is>
@@ -3602,16 +3602,16 @@
         <v>6</v>
       </c>
       <c r="T32" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="U32" t="n">
         <v>4</v>
       </c>
       <c r="V32" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="W32" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
     </row>
     <row r="33">
@@ -3633,22 +3633,22 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_35.jpg</t>
+          <t>stimuli/chair/chair_16.jpg</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_18.jpg</t>
+          <t>stimuli/ball/ball_23.jpg</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>stimuli/guitar/guitar_10.jpg</t>
+          <t>stimuli/phone/phone_04.jpg</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_28.jpg</t>
+          <t>stimuli/bicycle/bicycle_35.jpg</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -3658,17 +3658,17 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>guitar</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -3704,13 +3704,13 @@
         <v>4</v>
       </c>
       <c r="U33" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="V33" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="W33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34">
@@ -3732,47 +3732,47 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_18.jpg</t>
+          <t>stimuli/ball/ball_23.jpg</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_06.jpg</t>
+          <t>stimuli/flower/flower_22.jpg</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_07.jpg</t>
+          <t>stimuli/key/key_10.jpg</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_49.jpg</t>
+          <t>stimuli/dog/dog_30.jpg</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
+          <t>ball</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>flower</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>key</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
           <t>dog</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>flower</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>lamp</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>bread</t>
-        </is>
-      </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -3782,34 +3782,34 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P34" t="n">
-        <v>0.4</v>
+        <v>0.58</v>
       </c>
       <c r="Q34" t="n">
         <v>0.2</v>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S34" t="n">
         <v>8</v>
       </c>
       <c r="T34" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="U34" t="n">
         <v>6</v>
       </c>
       <c r="V34" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="W34" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="35">
@@ -3831,22 +3831,22 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_06.jpg</t>
+          <t>stimuli/flower/flower_22.jpg</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_02.jpg</t>
+          <t>stimuli/hammer/hammer_26.jpg</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>stimuli/house/house_25.jpg</t>
+          <t>stimuli/bicycle/bicycle_35.jpg</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>stimuli/key/key_14.jpg</t>
+          <t>stimuli/chair/chair_16.jpg</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -3861,17 +3861,17 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -3881,18 +3881,18 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P35" t="n">
-        <v>0.75</v>
+        <v>0.4</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.64</v>
+        <v>0.2</v>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S35" t="n">
@@ -3905,10 +3905,10 @@
         <v>7</v>
       </c>
       <c r="V35" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="W35" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
     </row>
     <row r="36">
@@ -3930,22 +3930,22 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_02.jpg</t>
+          <t>stimuli/hammer/hammer_26.jpg</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_42.jpg</t>
+          <t>stimuli/jacket/jacket_35.jpg</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>stimuli/key/key_14.jpg</t>
+          <t>stimuli/bread/bread_49.jpg</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_18.jpg</t>
+          <t>stimuli/lamp/lamp_08.jpg</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -3955,43 +3955,43 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>lamp</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P36" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.75</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.2</v>
+        <v>0.53</v>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S36" t="n">
@@ -4001,13 +4001,13 @@
         <v>7</v>
       </c>
       <c r="U36" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="V36" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="W36" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="37">
@@ -4029,84 +4029,84 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_42.jpg</t>
+          <t>stimuli/jacket/jacket_35.jpg</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>stimuli/house/house_25.jpg</t>
+          <t>stimuli/hand/hand_30.jpg</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>stimuli/pencil/pencil_25.jpg</t>
+          <t>stimuli/lamp/lamp_08.jpg</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_06.jpg</t>
+          <t>stimuli/house/house_05.jpg</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
+          <t>jacket</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
           <t>hand</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr">
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>lamp</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
         <is>
           <t>house</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>pencil</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>flower</t>
-        </is>
-      </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P37" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.6</v>
       </c>
       <c r="Q37" t="n">
-        <v>0.2</v>
+        <v>0.47</v>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S37" t="n">
         <v>11</v>
       </c>
       <c r="T37" t="n">
+        <v>10</v>
+      </c>
+      <c r="U37" t="n">
         <v>8</v>
       </c>
-      <c r="U37" t="n">
+      <c r="V37" t="n">
+        <v>14</v>
+      </c>
+      <c r="W37" t="n">
         <v>9</v>
-      </c>
-      <c r="V37" t="n">
-        <v>16</v>
-      </c>
-      <c r="W37" t="n">
-        <v>6</v>
       </c>
     </row>
     <row r="38">
@@ -4128,47 +4128,47 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>stimuli/house/house_25.jpg</t>
+          <t>stimuli/hand/hand_30.jpg</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_25.jpg</t>
+          <t>stimuli/bread/bread_49.jpg</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>stimuli/guitar/guitar_10.jpg</t>
+          <t>stimuli/bicycle/bicycle_35.jpg</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_02.jpg</t>
+          <t>stimuli/flower/flower_22.jpg</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>guitar</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -4178,34 +4178,34 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P38" t="n">
-        <v>0.73</v>
+        <v>0.6</v>
       </c>
       <c r="Q38" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S38" t="n">
         <v>12</v>
       </c>
       <c r="T38" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U38" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="V38" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="W38" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="39">
@@ -4227,27 +4227,27 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_25.jpg</t>
+          <t>stimuli/bread/bread_49.jpg</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>stimuli/key/key_14.jpg</t>
+          <t>stimuli/key/key_10.jpg</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_49.jpg</t>
+          <t>stimuli/phone/phone_04.jpg</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_06.jpg</t>
+          <t>stimuli/dog/dog_30.jpg</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -4257,12 +4257,12 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -4281,10 +4281,10 @@
         </is>
       </c>
       <c r="P39" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="Q39" t="n">
         <v>0.53</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>0.33</v>
       </c>
       <c r="R39" t="inlineStr">
         <is>
@@ -4295,16 +4295,16 @@
         <v>13</v>
       </c>
       <c r="T39" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="U39" t="n">
         <v>15</v>
       </c>
       <c r="V39" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="W39" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="40">
@@ -4326,22 +4326,22 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>stimuli/key/key_14.jpg</t>
+          <t>stimuli/key/key_10.jpg</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>stimuli/pencil/pencil_25.jpg</t>
+          <t>stimuli/glasses/glasses_02.jpg</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_07.jpg</t>
+          <t>stimuli/lamp/lamp_08.jpg</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_18.jpg</t>
+          <t>stimuli/hammer/hammer_26.jpg</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -4351,7 +4351,7 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>pencil</t>
+          <t>glasses</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -4361,12 +4361,12 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -4376,18 +4376,18 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P40" t="n">
         <v>0.8</v>
       </c>
       <c r="Q40" t="n">
-        <v>0.47</v>
+        <v>0.33</v>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S40" t="n">
@@ -4397,13 +4397,13 @@
         <v>15</v>
       </c>
       <c r="U40" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="V40" t="n">
         <v>14</v>
       </c>
       <c r="W40" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="41">
@@ -4425,32 +4425,32 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>stimuli/pencil/pencil_23.jpg</t>
+          <t>stimuli/lamp/lamp_30.jpg</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>stimuli/guitar/guitar_26.jpg</t>
+          <t>stimuli/car/car_04.jpg</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_39.jpg</t>
+          <t>stimuli/dog/dog_11.jpg</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_41.jpg</t>
+          <t>stimuli/hammer/hammer_09.jpg</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>pencil</t>
+          <t>lamp</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>guitar</t>
+          <t>car</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -4460,12 +4460,12 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>lamp</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -4475,34 +4475,34 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P41" t="n">
-        <v>0.42</v>
+        <v>0.8</v>
       </c>
       <c r="Q41" t="n">
-        <v>0.25</v>
+        <v>0.31</v>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S41" t="n">
         <v>2</v>
       </c>
       <c r="T41" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="U41" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="V41" t="n">
         <v>5</v>
       </c>
       <c r="W41" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
     </row>
     <row r="42">
@@ -4524,47 +4524,47 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>stimuli/guitar/guitar_26.jpg</t>
+          <t>stimuli/car/car_04.jpg</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_01.jpg</t>
+          <t>stimuli/dog/dog_11.jpg</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_04.jpg</t>
+          <t>stimuli/chair/chair_04.jpg</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>stimuli/key/key_13.jpg</t>
+          <t>stimuli/phone/phone_22.jpg</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>guitar</t>
+          <t>car</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -4574,34 +4574,34 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P42" t="n">
-        <v>0.58</v>
+        <v>0.64</v>
       </c>
       <c r="Q42" t="n">
-        <v>0.25</v>
+        <v>0.31</v>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S42" t="n">
         <v>3</v>
       </c>
       <c r="T42" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="U42" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="V42" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="W42" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="43">
@@ -4623,42 +4623,42 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_01.jpg</t>
+          <t>stimuli/dog/dog_11.jpg</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_30.jpg</t>
+          <t>stimuli/bread/bread_25.jpg</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_03.jpg</t>
+          <t>stimuli/jacket/jacket_06.jpg</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_22.jpg</t>
+          <t>stimuli/ball/ball_04.jpg</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
+          <t>dog</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
           <t>bread</t>
         </is>
       </c>
-      <c r="J43" t="inlineStr">
+      <c r="K43" t="inlineStr">
         <is>
           <t>jacket</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>flower</t>
-        </is>
-      </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -4677,10 +4677,10 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="Q43" t="n">
-        <v>0.42</v>
+        <v>0.53</v>
       </c>
       <c r="R43" t="inlineStr">
         <is>
@@ -4691,16 +4691,16 @@
         <v>4</v>
       </c>
       <c r="T43" t="n">
+        <v>5</v>
+      </c>
+      <c r="U43" t="n">
         <v>3</v>
       </c>
-      <c r="U43" t="n">
+      <c r="V43" t="n">
         <v>10</v>
       </c>
-      <c r="V43" t="n">
-        <v>6</v>
-      </c>
       <c r="W43" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -4722,52 +4722,52 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_30.jpg</t>
+          <t>stimuli/bread/bread_25.jpg</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_10.jpg</t>
+          <t>stimuli/jacket/jacket_06.jpg</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>stimuli/house/house_15.jpg</t>
+          <t>stimuli/bicycle/bicycle_28.jpg</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_41.jpg</t>
+          <t>stimuli/house/house_10.jpg</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
+          <t>bread</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
           <t>jacket</t>
         </is>
       </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>hand</t>
-        </is>
-      </c>
       <c r="K44" t="inlineStr">
         <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
           <t>house</t>
         </is>
       </c>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>lamp</t>
-        </is>
-      </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
@@ -4776,30 +4776,30 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>0.64</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="Q44" t="n">
-        <v>0.42</v>
+        <v>0.53</v>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S44" t="n">
         <v>5</v>
       </c>
       <c r="T44" t="n">
+        <v>3</v>
+      </c>
+      <c r="U44" t="n">
         <v>10</v>
       </c>
-      <c r="U44" t="n">
-        <v>8</v>
-      </c>
       <c r="V44" t="n">
+        <v>2</v>
+      </c>
+      <c r="W44" t="n">
         <v>9</v>
-      </c>
-      <c r="W44" t="n">
-        <v>14</v>
       </c>
     </row>
     <row r="45">
@@ -4821,42 +4821,42 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_10.jpg</t>
+          <t>stimuli/jacket/jacket_06.jpg</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_03.jpg</t>
+          <t>stimuli/flower/flower_21.jpg</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_44.jpg</t>
+          <t>stimuli/hand/hand_20.jpg</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>stimuli/key/key_13.jpg</t>
+          <t>stimuli/phone/phone_22.jpg</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
+          <t>jacket</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>flower</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
           <t>hand</t>
         </is>
       </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>flower</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>bicycle</t>
-        </is>
-      </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -4875,10 +4875,10 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>0.58</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="Q45" t="n">
-        <v>0.42</v>
+        <v>0.47</v>
       </c>
       <c r="R45" t="inlineStr">
         <is>
@@ -4889,16 +4889,16 @@
         <v>6</v>
       </c>
       <c r="T45" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U45" t="n">
         <v>6</v>
       </c>
       <c r="V45" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="W45" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="46">
@@ -4920,22 +4920,22 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_03.jpg</t>
+          <t>stimuli/flower/flower_21.jpg</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_13.jpg</t>
+          <t>stimuli/chair/chair_04.jpg</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_39.jpg</t>
+          <t>stimuli/hammer/hammer_09.jpg</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_01.jpg</t>
+          <t>stimuli/pencil/pencil_15.jpg</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -4950,22 +4950,22 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>pencil</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
@@ -4974,14 +4974,14 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.58</v>
       </c>
       <c r="Q46" t="n">
-        <v>0.27</v>
+        <v>0.47</v>
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S46" t="n">
@@ -4994,10 +4994,10 @@
         <v>4</v>
       </c>
       <c r="V46" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="W46" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
     </row>
     <row r="47">
@@ -5019,22 +5019,22 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_13.jpg</t>
+          <t>stimuli/chair/chair_04.jpg</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
+          <t>stimuli/bicycle/bicycle_28.jpg</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
           <t>stimuli/ball/ball_04.jpg</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>stimuli/hammer/hammer_22.jpg</t>
-        </is>
-      </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>stimuli/guitar/guitar_26.jpg</t>
+          <t>stimuli/car/car_04.jpg</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -5044,17 +5044,17 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
           <t>ball</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>hammer</t>
-        </is>
-      </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>guitar</t>
+          <t>car</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -5064,16 +5064,16 @@
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P47" t="n">
-        <v>0.64</v>
+        <v>0.75</v>
       </c>
       <c r="Q47" t="n">
         <v>0.4</v>
@@ -5090,13 +5090,13 @@
         <v>4</v>
       </c>
       <c r="U47" t="n">
+        <v>2</v>
+      </c>
+      <c r="V47" t="n">
         <v>1</v>
       </c>
-      <c r="V47" t="n">
-        <v>7</v>
-      </c>
       <c r="W47" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="48">
@@ -5118,52 +5118,52 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_04.jpg</t>
+          <t>stimuli/bicycle/bicycle_28.jpg</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>stimuli/house/house_15.jpg</t>
+          <t>stimuli/hand/hand_20.jpg</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_41.jpg</t>
+          <t>stimuli/house/house_10.jpg</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>stimuli/pencil/pencil_23.jpg</t>
+          <t>stimuli/flower/flower_21.jpg</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
+          <t>hand</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
           <t>house</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>lamp</t>
-        </is>
-      </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>pencil</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
@@ -5172,30 +5172,30 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>0.64</v>
+        <v>0.75</v>
       </c>
       <c r="Q48" t="n">
-        <v>0.53</v>
+        <v>0.2</v>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S48" t="n">
         <v>9</v>
       </c>
       <c r="T48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U48" t="n">
+        <v>8</v>
+      </c>
+      <c r="V48" t="n">
         <v>9</v>
       </c>
-      <c r="V48" t="n">
-        <v>14</v>
-      </c>
       <c r="W48" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="49">
@@ -5217,37 +5217,37 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>stimuli/house/house_15.jpg</t>
+          <t>stimuli/hand/hand_20.jpg</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_39.jpg</t>
+          <t>stimuli/ball/ball_04.jpg</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_01.jpg</t>
+          <t>stimuli/lamp/lamp_30.jpg</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_13.jpg</t>
+          <t>stimuli/chair/chair_04.jpg</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>lamp</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -5257,12 +5257,12 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
@@ -5271,27 +5271,27 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>0.47</v>
+        <v>0.6</v>
       </c>
       <c r="Q49" t="n">
         <v>0.2</v>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S49" t="n">
         <v>10</v>
       </c>
       <c r="T49" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U49" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="V49" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="W49" t="n">
         <v>4</v>
@@ -5316,42 +5316,42 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_39.jpg</t>
+          <t>stimuli/ball/ball_04.jpg</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_44.jpg</t>
+          <t>stimuli/house/house_10.jpg</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>stimuli/guitar/guitar_26.jpg</t>
+          <t>stimuli/bread/bread_25.jpg</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_30.jpg</t>
+          <t>stimuli/flower/flower_21.jpg</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>house</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>guitar</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -5370,10 +5370,10 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>0.6</v>
+        <v>0.47</v>
       </c>
       <c r="Q50" t="n">
-        <v>0.47</v>
+        <v>0.33</v>
       </c>
       <c r="R50" t="inlineStr">
         <is>
@@ -5384,16 +5384,16 @@
         <v>11</v>
       </c>
       <c r="T50" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="U50" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="V50" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="W50" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="51">
@@ -5415,27 +5415,27 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_44.jpg</t>
+          <t>stimuli/house/house_10.jpg</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_22.jpg</t>
+          <t>stimuli/hammer/hammer_09.jpg</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>stimuli/pencil/pencil_23.jpg</t>
+          <t>stimuli/chair/chair_04.jpg</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_10.jpg</t>
+          <t>stimuli/hand/hand_20.jpg</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>house</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -5445,7 +5445,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>pencil</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -5460,19 +5460,19 @@
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P51" t="n">
-        <v>0.73</v>
+        <v>0.33</v>
       </c>
       <c r="Q51" t="n">
-        <v>0.47</v>
+        <v>0.2</v>
       </c>
       <c r="R51" t="inlineStr">
         <is>
@@ -5483,13 +5483,13 @@
         <v>12</v>
       </c>
       <c r="T51" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="U51" t="n">
         <v>7</v>
       </c>
       <c r="V51" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="W51" t="n">
         <v>8</v>
@@ -5514,22 +5514,22 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_22.jpg</t>
+          <t>stimuli/hammer/hammer_09.jpg</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_41.jpg</t>
+          <t>stimuli/phone/phone_22.jpg</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_01.jpg</t>
+          <t>stimuli/dog/dog_11.jpg</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_04.jpg</t>
+          <t>stimuli/bicycle/bicycle_28.jpg</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -5539,27 +5539,27 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>lamp</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
@@ -5575,7 +5575,7 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S52" t="n">
@@ -5585,13 +5585,13 @@
         <v>7</v>
       </c>
       <c r="U52" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="V52" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="W52" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="53">
@@ -5613,84 +5613,84 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_41.jpg</t>
+          <t>stimuli/phone/phone_22.jpg</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>stimuli/key/key_13.jpg</t>
+          <t>stimuli/pencil/pencil_15.jpg</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>stimuli/guitar/guitar_26.jpg</t>
+          <t>stimuli/bread/bread_25.jpg</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_39.jpg</t>
+          <t>stimuli/ball/ball_04.jpg</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>lamp</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>pencil</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>guitar</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P53" t="n">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="Q53" t="n">
         <v>0.27</v>
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S53" t="n">
         <v>14</v>
       </c>
       <c r="T53" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="U53" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="V53" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="W53" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -5712,27 +5712,27 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>stimuli/guitar/guitar_10.jpg</t>
+          <t>stimuli/phone/phone_04.jpg</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_07.jpg</t>
+          <t>stimuli/lamp/lamp_08.jpg</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>stimuli/house/house_25.jpg</t>
+          <t>stimuli/bicycle/bicycle_35.jpg</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>stimuli/key/key_14.jpg</t>
+          <t>stimuli/key/key_10.jpg</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>guitar</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -5742,7 +5742,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -5752,41 +5752,41 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P54" t="n">
-        <v>0.36</v>
+        <v>0.8</v>
       </c>
       <c r="Q54" t="n">
         <v>0.25</v>
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S54" t="n">
         <v>2</v>
       </c>
       <c r="T54" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="U54" t="n">
         <v>14</v>
       </c>
       <c r="V54" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="W54" t="n">
         <v>15</v>
@@ -5811,22 +5811,22 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_07.jpg</t>
+          <t>stimuli/lamp/lamp_08.jpg</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_28.jpg</t>
+          <t>stimuli/bicycle/bicycle_35.jpg</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_49.jpg</t>
+          <t>stimuli/dog/dog_30.jpg</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>stimuli/pencil/pencil_25.jpg</t>
+          <t>stimuli/glasses/glasses_02.jpg</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -5836,22 +5836,22 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>pencil</t>
+          <t>glasses</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -5861,7 +5861,7 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P55" t="n">
@@ -5872,7 +5872,7 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S55" t="n">
@@ -5882,13 +5882,13 @@
         <v>14</v>
       </c>
       <c r="U55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V55" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="W55" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="56">
@@ -5910,42 +5910,42 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_28.jpg</t>
+          <t>stimuli/bicycle/bicycle_35.jpg</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_19.jpg</t>
+          <t>stimuli/house/house_05.jpg</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_35.jpg</t>
+          <t>stimuli/jacket/jacket_35.jpg</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>stimuli/guitar/guitar_10.jpg</t>
+          <t>stimuli/bread/bread_49.jpg</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>house</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>guitar</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -5955,19 +5955,19 @@
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P56" t="n">
-        <v>0.75</v>
+        <v>0.53</v>
       </c>
       <c r="Q56" t="n">
-        <v>0.2</v>
+        <v>0.42</v>
       </c>
       <c r="R56" t="inlineStr">
         <is>
@@ -5978,16 +5978,16 @@
         <v>4</v>
       </c>
       <c r="T56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U56" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="V56" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="W56" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="57">
@@ -6009,42 +6009,42 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_19.jpg</t>
+          <t>stimuli/house/house_05.jpg</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_49.jpg</t>
+          <t>stimuli/dog/dog_30.jpg</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_25.jpg</t>
+          <t>stimuli/hammer/hammer_26.jpg</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>stimuli/pencil/pencil_25.jpg</t>
+          <t>stimuli/key/key_10.jpg</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>house</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>pencil</t>
+          <t>key</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
@@ -6063,10 +6063,10 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>0.47</v>
+        <v>0.64</v>
       </c>
       <c r="Q57" t="n">
-        <v>0.36</v>
+        <v>0.42</v>
       </c>
       <c r="R57" t="inlineStr">
         <is>
@@ -6077,16 +6077,16 @@
         <v>5</v>
       </c>
       <c r="T57" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="U57" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="V57" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="W57" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="58">
@@ -6108,27 +6108,27 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_49.jpg</t>
+          <t>stimuli/dog/dog_30.jpg</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_35.jpg</t>
+          <t>stimuli/chair/chair_16.jpg</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_18.jpg</t>
+          <t>stimuli/ball/ball_23.jpg</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_42.jpg</t>
+          <t>stimuli/glasses/glasses_02.jpg</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -6138,12 +6138,12 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>glasses</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
@@ -6153,19 +6153,19 @@
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P58" t="n">
         <v>0.8</v>
       </c>
       <c r="Q58" t="n">
-        <v>0.64</v>
+        <v>0.42</v>
       </c>
       <c r="R58" t="inlineStr">
         <is>
@@ -6176,16 +6176,16 @@
         <v>6</v>
       </c>
       <c r="T58" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="U58" t="n">
         <v>4</v>
       </c>
       <c r="V58" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="W58" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
     </row>
     <row r="59">
@@ -6207,22 +6207,22 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_35.jpg</t>
+          <t>stimuli/chair/chair_16.jpg</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_18.jpg</t>
+          <t>stimuli/ball/ball_23.jpg</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_06.jpg</t>
+          <t>stimuli/flower/flower_22.jpg</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_25.jpg</t>
+          <t>stimuli/hand/hand_30.jpg</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -6232,7 +6232,7 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -6257,18 +6257,18 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P59" t="n">
         <v>0.8</v>
       </c>
       <c r="Q59" t="n">
-        <v>0.58</v>
+        <v>0.64</v>
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S59" t="n">
@@ -6278,13 +6278,13 @@
         <v>4</v>
       </c>
       <c r="U59" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="V59" t="n">
         <v>6</v>
       </c>
       <c r="W59" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="60">
@@ -6306,27 +6306,27 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_18.jpg</t>
+          <t>stimuli/ball/ball_23.jpg</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_06.jpg</t>
+          <t>stimuli/flower/flower_22.jpg</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>stimuli/key/key_14.jpg</t>
+          <t>stimuli/phone/phone_04.jpg</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_19.jpg</t>
+          <t>stimuli/house/house_05.jpg</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -6336,54 +6336,54 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>house</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P60" t="n">
-        <v>0.58</v>
+        <v>0.47</v>
       </c>
       <c r="Q60" t="n">
         <v>0.27</v>
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S60" t="n">
         <v>8</v>
       </c>
       <c r="T60" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="U60" t="n">
         <v>6</v>
       </c>
       <c r="V60" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="W60" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="61">
@@ -6405,22 +6405,22 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_06.jpg</t>
+          <t>stimuli/flower/flower_22.jpg</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_02.jpg</t>
+          <t>stimuli/hammer/hammer_26.jpg</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_07.jpg</t>
+          <t>stimuli/bicycle/bicycle_35.jpg</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_35.jpg</t>
+          <t>stimuli/chair/chair_16.jpg</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -6435,7 +6435,7 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>lamp</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -6459,7 +6459,7 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>0.47</v>
+        <v>0.4</v>
       </c>
       <c r="Q61" t="n">
         <v>0.2</v>
@@ -6479,7 +6479,7 @@
         <v>7</v>
       </c>
       <c r="V61" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="W61" t="n">
         <v>4</v>
@@ -6504,22 +6504,22 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_02.jpg</t>
+          <t>stimuli/hammer/hammer_26.jpg</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_42.jpg</t>
+          <t>stimuli/jacket/jacket_35.jpg</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_25.jpg</t>
+          <t>stimuli/lamp/lamp_08.jpg</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_28.jpg</t>
+          <t>stimuli/ball/ball_23.jpg</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>lamp</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -6544,7 +6544,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
@@ -6554,18 +6554,18 @@
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P62" t="n">
-        <v>0.75</v>
+        <v>0.53</v>
       </c>
       <c r="Q62" t="n">
-        <v>0.47</v>
+        <v>0.2</v>
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S62" t="n">
@@ -6575,10 +6575,10 @@
         <v>7</v>
       </c>
       <c r="U62" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="V62" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="W62" t="n">
         <v>1</v>
@@ -6603,47 +6603,47 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_42.jpg</t>
+          <t>stimuli/jacket/jacket_35.jpg</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>stimuli/house/house_25.jpg</t>
+          <t>stimuli/hand/hand_30.jpg</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_35.jpg</t>
+          <t>stimuli/bicycle/bicycle_35.jpg</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_06.jpg</t>
+          <t>stimuli/dog/dog_30.jpg</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
+          <t>jacket</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
           <t>hand</t>
         </is>
       </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>house</t>
-        </is>
-      </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -6653,34 +6653,34 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P63" t="n">
-        <v>0.33</v>
+        <v>0.53</v>
       </c>
       <c r="Q63" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S63" t="n">
         <v>11</v>
       </c>
       <c r="T63" t="n">
+        <v>10</v>
+      </c>
+      <c r="U63" t="n">
         <v>8</v>
       </c>
-      <c r="U63" t="n">
-        <v>9</v>
-      </c>
       <c r="V63" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="W63" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="64">
@@ -6702,32 +6702,32 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>stimuli/house/house_25.jpg</t>
+          <t>stimuli/hand/hand_30.jpg</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_25.jpg</t>
+          <t>stimuli/bread/bread_49.jpg</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>stimuli/key/key_14.jpg</t>
+          <t>stimuli/key/key_10.jpg</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_02.jpg</t>
+          <t>stimuli/flower/flower_22.jpg</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -6752,34 +6752,34 @@
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P64" t="n">
         <v>0.8</v>
       </c>
       <c r="Q64" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S64" t="n">
         <v>12</v>
       </c>
       <c r="T64" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U64" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="V64" t="n">
         <v>15</v>
       </c>
       <c r="W64" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="65">
@@ -6801,27 +6801,27 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_25.jpg</t>
+          <t>stimuli/bread/bread_49.jpg</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>stimuli/key/key_14.jpg</t>
+          <t>stimuli/key/key_10.jpg</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>stimuli/guitar/guitar_10.jpg</t>
+          <t>stimuli/house/house_05.jpg</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_18.jpg</t>
+          <t>stimuli/ball/ball_23.jpg</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>guitar</t>
+          <t>house</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -6846,16 +6846,16 @@
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P65" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="Q65" t="n">
         <v>0.4</v>
@@ -6869,16 +6869,16 @@
         <v>13</v>
       </c>
       <c r="T65" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="U65" t="n">
         <v>15</v>
       </c>
       <c r="V65" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="W65" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="66">
@@ -6900,22 +6900,22 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>stimuli/key/key_14.jpg</t>
+          <t>stimuli/key/key_10.jpg</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>stimuli/pencil/pencil_25.jpg</t>
+          <t>stimuli/glasses/glasses_02.jpg</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_06.jpg</t>
+          <t>stimuli/lamp/lamp_08.jpg</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>stimuli/guitar/guitar_10.jpg</t>
+          <t>stimuli/jacket/jacket_35.jpg</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -6925,43 +6925,43 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>pencil</t>
+          <t>glasses</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>lamp</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>guitar</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P66" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="Q66" t="n">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S66" t="n">
@@ -6971,13 +6971,13 @@
         <v>15</v>
       </c>
       <c r="U66" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="V66" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="W66" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="67">
@@ -6999,47 +6999,47 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>stimuli/pencil/pencil_23.jpg</t>
+          <t>stimuli/lamp/lamp_30.jpg</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>stimuli/guitar/guitar_26.jpg</t>
+          <t>stimuli/car/car_04.jpg</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_39.jpg</t>
+          <t>stimuli/jacket/jacket_06.jpg</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>stimuli/key/key_13.jpg</t>
+          <t>stimuli/hammer/hammer_09.jpg</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>pencil</t>
+          <t>lamp</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>guitar</t>
+          <t>car</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
@@ -7049,34 +7049,34 @@
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P67" t="n">
-        <v>0.42</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="Q67" t="n">
-        <v>0.2</v>
+        <v>0.31</v>
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S67" t="n">
         <v>2</v>
       </c>
       <c r="T67" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="U67" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="V67" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="W67" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="68">
@@ -7098,47 +7098,47 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>stimuli/guitar/guitar_26.jpg</t>
+          <t>stimuli/car/car_04.jpg</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_01.jpg</t>
+          <t>stimuli/dog/dog_11.jpg</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>stimuli/house/house_15.jpg</t>
+          <t>stimuli/flower/flower_21.jpg</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_22.jpg</t>
+          <t>stimuli/pencil/pencil_15.jpg</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>guitar</t>
+          <t>car</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>pencil</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
@@ -7148,34 +7148,34 @@
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P68" t="n">
-        <v>0.53</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="Q68" t="n">
-        <v>0.36</v>
+        <v>0.25</v>
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S68" t="n">
         <v>3</v>
       </c>
       <c r="T68" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="U68" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="V68" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="W68" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
     </row>
     <row r="69">
@@ -7197,52 +7197,52 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_01.jpg</t>
+          <t>stimuli/dog/dog_11.jpg</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_30.jpg</t>
+          <t>stimuli/bread/bread_25.jpg</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_03.jpg</t>
+          <t>stimuli/hand/hand_20.jpg</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_41.jpg</t>
+          <t>stimuli/phone/phone_22.jpg</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
+          <t>dog</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
           <t>bread</t>
         </is>
       </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>jacket</t>
-        </is>
-      </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>lamp</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
@@ -7251,30 +7251,30 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>0.75</v>
+        <v>0.58</v>
       </c>
       <c r="Q69" t="n">
         <v>0.36</v>
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S69" t="n">
         <v>4</v>
       </c>
       <c r="T69" t="n">
+        <v>5</v>
+      </c>
+      <c r="U69" t="n">
         <v>3</v>
       </c>
-      <c r="U69" t="n">
-        <v>10</v>
-      </c>
       <c r="V69" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="W69" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="70">
@@ -7296,84 +7296,84 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_30.jpg</t>
+          <t>stimuli/bread/bread_25.jpg</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_10.jpg</t>
+          <t>stimuli/jacket/jacket_06.jpg</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_04.jpg</t>
+          <t>stimuli/chair/chair_04.jpg</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>stimuli/key/key_13.jpg</t>
+          <t>stimuli/lamp/lamp_30.jpg</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
+          <t>bread</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
           <t>jacket</t>
         </is>
       </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>hand</t>
-        </is>
-      </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>lamp</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P70" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.75</v>
       </c>
       <c r="Q70" t="n">
-        <v>0.36</v>
+        <v>0.27</v>
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S70" t="n">
         <v>5</v>
       </c>
       <c r="T70" t="n">
+        <v>3</v>
+      </c>
+      <c r="U70" t="n">
         <v>10</v>
       </c>
-      <c r="U70" t="n">
-        <v>8</v>
-      </c>
       <c r="V70" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="W70" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="71">
@@ -7395,27 +7395,27 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_10.jpg</t>
+          <t>stimuli/jacket/jacket_06.jpg</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_03.jpg</t>
+          <t>stimuli/flower/flower_21.jpg</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_13.jpg</t>
+          <t>stimuli/bicycle/bicycle_28.jpg</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_22.jpg</t>
+          <t>stimuli/pencil/pencil_15.jpg</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -7425,17 +7425,17 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>pencil</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
@@ -7445,34 +7445,34 @@
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P71" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="Q71" t="n">
-        <v>0.53</v>
+        <v>0.42</v>
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S71" t="n">
         <v>6</v>
       </c>
       <c r="T71" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U71" t="n">
         <v>6</v>
       </c>
       <c r="V71" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="W71" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
     </row>
     <row r="72">
@@ -7494,22 +7494,22 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_03.jpg</t>
+          <t>stimuli/flower/flower_21.jpg</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_13.jpg</t>
+          <t>stimuli/chair/chair_04.jpg</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_44.jpg</t>
+          <t>stimuli/lamp/lamp_30.jpg</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>stimuli/key/key_13.jpg</t>
+          <t>stimuli/dog/dog_11.jpg</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -7524,22 +7524,22 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>lamp</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
@@ -7548,14 +7548,14 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>0.64</v>
+        <v>0.4</v>
       </c>
       <c r="Q72" t="n">
-        <v>0.47</v>
+        <v>0.27</v>
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S72" t="n">
@@ -7568,10 +7568,10 @@
         <v>4</v>
       </c>
       <c r="V72" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="W72" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="73">
@@ -7593,22 +7593,22 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_13.jpg</t>
+          <t>stimuli/chair/chair_04.jpg</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
+          <t>stimuli/bicycle/bicycle_28.jpg</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
           <t>stimuli/ball/ball_04.jpg</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>stimuli/lamp/lamp_41.jpg</t>
-        </is>
-      </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_01.jpg</t>
+          <t>stimuli/phone/phone_22.jpg</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -7618,43 +7618,43 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
           <t>ball</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t>lamp</t>
-        </is>
-      </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P73" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="Q73" t="n">
         <v>0.58</v>
       </c>
-      <c r="Q73" t="n">
-        <v>0.33</v>
-      </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S73" t="n">
@@ -7664,13 +7664,13 @@
         <v>4</v>
       </c>
       <c r="U73" t="n">
+        <v>2</v>
+      </c>
+      <c r="V73" t="n">
         <v>1</v>
       </c>
-      <c r="V73" t="n">
-        <v>14</v>
-      </c>
       <c r="W73" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
     </row>
     <row r="74">
@@ -7692,37 +7692,37 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_04.jpg</t>
+          <t>stimuli/bicycle/bicycle_28.jpg</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>stimuli/house/house_15.jpg</t>
+          <t>stimuli/hand/hand_20.jpg</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>stimuli/key/key_13.jpg</t>
+          <t>stimuli/car/car_04.jpg</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_30.jpg</t>
+          <t>stimuli/jacket/jacket_06.jpg</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>car</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -7746,10 +7746,10 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>0.58</v>
+        <v>0.47</v>
       </c>
       <c r="Q74" t="n">
-        <v>0.33</v>
+        <v>0.27</v>
       </c>
       <c r="R74" t="inlineStr">
         <is>
@@ -7760,13 +7760,13 @@
         <v>9</v>
       </c>
       <c r="T74" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U74" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V74" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="W74" t="n">
         <v>10</v>
@@ -7791,42 +7791,42 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>stimuli/house/house_15.jpg</t>
+          <t>stimuli/hand/hand_20.jpg</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_39.jpg</t>
+          <t>stimuli/ball/ball_04.jpg</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_10.jpg</t>
+          <t>stimuli/hammer/hammer_09.jpg</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_13.jpg</t>
+          <t>stimuli/bread/bread_25.jpg</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
@@ -7836,19 +7836,19 @@
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P75" t="n">
-        <v>0.33</v>
+        <v>0.75</v>
       </c>
       <c r="Q75" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="R75" t="inlineStr">
         <is>
@@ -7859,16 +7859,16 @@
         <v>10</v>
       </c>
       <c r="T75" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U75" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="V75" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W75" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="76">
@@ -7890,84 +7890,84 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_39.jpg</t>
+          <t>stimuli/ball/ball_04.jpg</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_44.jpg</t>
+          <t>stimuli/house/house_10.jpg</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>stimuli/guitar/guitar_26.jpg</t>
+          <t>stimuli/car/car_04.jpg</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_04.jpg</t>
+          <t>stimuli/flower/flower_21.jpg</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>house</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>guitar</t>
+          <t>car</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P76" t="n">
         <v>0.6</v>
       </c>
       <c r="Q76" t="n">
-        <v>0.2</v>
+        <v>0.33</v>
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S76" t="n">
         <v>11</v>
       </c>
       <c r="T76" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="U76" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="V76" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="W76" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="77">
@@ -7989,27 +7989,27 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_44.jpg</t>
+          <t>stimuli/house/house_10.jpg</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_22.jpg</t>
+          <t>stimuli/hammer/hammer_09.jpg</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>stimuli/pencil/pencil_23.jpg</t>
+          <t>stimuli/bread/bread_25.jpg</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_13.jpg</t>
+          <t>stimuli/chair/chair_04.jpg</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>house</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -8019,7 +8019,7 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>pencil</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -8029,41 +8029,41 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P77" t="n">
-        <v>0.73</v>
+        <v>0.53</v>
       </c>
       <c r="Q77" t="n">
         <v>0.33</v>
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S77" t="n">
         <v>12</v>
       </c>
       <c r="T77" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="U77" t="n">
         <v>7</v>
       </c>
       <c r="V77" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="W77" t="n">
         <v>4</v>
@@ -8088,22 +8088,22 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_22.jpg</t>
+          <t>stimuli/hammer/hammer_09.jpg</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_41.jpg</t>
+          <t>stimuli/phone/phone_22.jpg</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_01.jpg</t>
+          <t>stimuli/dog/dog_11.jpg</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>stimuli/house/house_15.jpg</t>
+          <t>stimuli/flower/flower_21.jpg</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -8113,22 +8113,22 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>lamp</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
@@ -8138,18 +8138,18 @@
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P78" t="n">
         <v>0.67</v>
       </c>
       <c r="Q78" t="n">
-        <v>0.27</v>
+        <v>0.47</v>
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S78" t="n">
@@ -8159,13 +8159,13 @@
         <v>7</v>
       </c>
       <c r="U78" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="V78" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="W78" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="79">
@@ -8187,52 +8187,52 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_41.jpg</t>
+          <t>stimuli/phone/phone_22.jpg</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>stimuli/key/key_13.jpg</t>
+          <t>stimuli/pencil/pencil_15.jpg</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_10.jpg</t>
+          <t>stimuli/bread/bread_25.jpg</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_04.jpg</t>
+          <t>stimuli/house/house_10.jpg</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>lamp</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>pencil</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>house</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O79" t="inlineStr">
@@ -8241,30 +8241,30 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>0.6</v>
+        <v>0.67</v>
       </c>
       <c r="Q79" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S79" t="n">
         <v>14</v>
       </c>
       <c r="T79" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="U79" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="V79" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="W79" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="80">
@@ -8286,27 +8286,27 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>stimuli/guitar/guitar_10.jpg</t>
+          <t>stimuli/phone/phone_04.jpg</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_07.jpg</t>
+          <t>stimuli/lamp/lamp_08.jpg</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_28.jpg</t>
+          <t>stimuli/flower/flower_22.jpg</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_42.jpg</t>
+          <t>stimuli/hand/hand_30.jpg</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>guitar</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -8316,7 +8316,7 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -8340,10 +8340,10 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>0.8</v>
+        <v>0.53</v>
       </c>
       <c r="Q80" t="n">
-        <v>0.42</v>
+        <v>0.36</v>
       </c>
       <c r="R80" t="inlineStr">
         <is>
@@ -8354,13 +8354,13 @@
         <v>2</v>
       </c>
       <c r="T80" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="U80" t="n">
         <v>14</v>
       </c>
       <c r="V80" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="W80" t="n">
         <v>8</v>
@@ -8385,22 +8385,22 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_07.jpg</t>
+          <t>stimuli/lamp/lamp_08.jpg</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_28.jpg</t>
+          <t>stimuli/bicycle/bicycle_35.jpg</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_42.jpg</t>
+          <t>stimuli/jacket/jacket_35.jpg</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>stimuli/key/key_14.jpg</t>
+          <t>stimuli/bread/bread_49.jpg</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -8410,17 +8410,17 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
@@ -8430,19 +8430,19 @@
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P81" t="n">
         <v>0.47</v>
       </c>
       <c r="Q81" t="n">
-        <v>0.31</v>
+        <v>0.36</v>
       </c>
       <c r="R81" t="inlineStr">
         <is>
@@ -8456,13 +8456,13 @@
         <v>14</v>
       </c>
       <c r="U81" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V81" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W81" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
     </row>
     <row r="82">
@@ -8484,52 +8484,52 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_28.jpg</t>
+          <t>stimuli/bicycle/bicycle_35.jpg</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_19.jpg</t>
+          <t>stimuli/house/house_05.jpg</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_18.jpg</t>
+          <t>stimuli/flower/flower_22.jpg</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_25.jpg</t>
+          <t>stimuli/key/key_10.jpg</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>house</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>key</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O82" t="inlineStr">
@@ -8538,30 +8538,30 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="Q82" t="n">
-        <v>0.42</v>
+        <v>0.36</v>
       </c>
       <c r="R82" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S82" t="n">
         <v>4</v>
       </c>
       <c r="T82" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U82" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="V82" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W82" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="83">
@@ -8583,42 +8583,42 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_19.jpg</t>
+          <t>stimuli/house/house_05.jpg</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_49.jpg</t>
+          <t>stimuli/dog/dog_30.jpg</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_02.jpg</t>
+          <t>stimuli/chair/chair_16.jpg</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>stimuli/pencil/pencil_25.jpg</t>
+          <t>stimuli/glasses/glasses_02.jpg</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>house</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>pencil</t>
+          <t>glasses</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
@@ -8628,16 +8628,16 @@
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P83" t="n">
-        <v>0.64</v>
+        <v>0.8</v>
       </c>
       <c r="Q83" t="n">
         <v>0.36</v>
@@ -8651,16 +8651,16 @@
         <v>5</v>
       </c>
       <c r="T83" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="U83" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="V83" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="W83" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="84">
@@ -8682,27 +8682,27 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_49.jpg</t>
+          <t>stimuli/dog/dog_30.jpg</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_35.jpg</t>
+          <t>stimuli/chair/chair_16.jpg</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>stimuli/guitar/guitar_10.jpg</t>
+          <t>stimuli/phone/phone_04.jpg</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_28.jpg</t>
+          <t>stimuli/bicycle/bicycle_35.jpg</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -8712,22 +8712,22 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>guitar</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O84" t="inlineStr">
@@ -8743,23 +8743,23 @@
       </c>
       <c r="R84" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S84" t="n">
         <v>6</v>
       </c>
       <c r="T84" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="U84" t="n">
         <v>4</v>
       </c>
       <c r="V84" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="W84" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="85">
@@ -8781,22 +8781,22 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_35.jpg</t>
+          <t>stimuli/chair/chair_16.jpg</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_18.jpg</t>
+          <t>stimuli/ball/ball_23.jpg</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_06.jpg</t>
+          <t>stimuli/hammer/hammer_26.jpg</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>stimuli/pencil/pencil_25.jpg</t>
+          <t>stimuli/key/key_10.jpg</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -8806,43 +8806,43 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>pencil</t>
+          <t>key</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P85" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="Q85" t="n">
-        <v>0.47</v>
+        <v>0.53</v>
       </c>
       <c r="R85" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S85" t="n">
@@ -8852,13 +8852,13 @@
         <v>4</v>
       </c>
       <c r="U85" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="V85" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W85" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="86">
@@ -8880,27 +8880,27 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_18.jpg</t>
+          <t>stimuli/ball/ball_23.jpg</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_06.jpg</t>
+          <t>stimuli/flower/flower_22.jpg</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>stimuli/house/house_25.jpg</t>
+          <t>stimuli/jacket/jacket_35.jpg</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>stimuli/key/key_14.jpg</t>
+          <t>stimuli/house/house_05.jpg</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -8910,14 +8910,14 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
+          <t>jacket</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
           <t>house</t>
         </is>
       </c>
-      <c r="L86" t="inlineStr">
-        <is>
-          <t>key</t>
-        </is>
-      </c>
       <c r="M86" t="inlineStr">
         <is>
           <t>right</t>
@@ -8934,10 +8934,10 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.75</v>
       </c>
       <c r="Q86" t="n">
-        <v>0.58</v>
+        <v>0.27</v>
       </c>
       <c r="R86" t="inlineStr">
         <is>
@@ -8948,16 +8948,16 @@
         <v>8</v>
       </c>
       <c r="T86" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="U86" t="n">
         <v>6</v>
       </c>
       <c r="V86" t="n">
+        <v>10</v>
+      </c>
+      <c r="W86" t="n">
         <v>9</v>
-      </c>
-      <c r="W86" t="n">
-        <v>15</v>
       </c>
     </row>
     <row r="87">
@@ -8979,22 +8979,22 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_06.jpg</t>
+          <t>stimuli/flower/flower_22.jpg</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_02.jpg</t>
+          <t>stimuli/hammer/hammer_26.jpg</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_19.jpg</t>
+          <t>stimuli/hand/hand_30.jpg</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_35.jpg</t>
+          <t>stimuli/lamp/lamp_08.jpg</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -9009,12 +9009,12 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>lamp</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
@@ -9024,19 +9024,19 @@
       </c>
       <c r="N87" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P87" t="n">
-        <v>0.33</v>
+        <v>0.75</v>
       </c>
       <c r="Q87" t="n">
-        <v>0.2</v>
+        <v>0.47</v>
       </c>
       <c r="R87" t="inlineStr">
         <is>
@@ -9053,10 +9053,10 @@
         <v>7</v>
       </c>
       <c r="V87" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="W87" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
     </row>
     <row r="88">
@@ -9078,22 +9078,22 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_02.jpg</t>
+          <t>stimuli/hammer/hammer_26.jpg</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_42.jpg</t>
+          <t>stimuli/jacket/jacket_35.jpg</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_49.jpg</t>
+          <t>stimuli/dog/dog_30.jpg</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_18.jpg</t>
+          <t>stimuli/ball/ball_23.jpg</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -9103,22 +9103,22 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
@@ -9128,7 +9128,7 @@
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P88" t="n">
@@ -9139,7 +9139,7 @@
       </c>
       <c r="R88" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S88" t="n">
@@ -9149,13 +9149,13 @@
         <v>7</v>
       </c>
       <c r="U88" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="V88" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="W88" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="89">
@@ -9177,84 +9177,84 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_42.jpg</t>
+          <t>stimuli/jacket/jacket_35.jpg</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>stimuli/house/house_25.jpg</t>
+          <t>stimuli/hand/hand_30.jpg</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>stimuli/key/key_14.jpg</t>
+          <t>stimuli/bread/bread_49.jpg</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_07.jpg</t>
+          <t>stimuli/glasses/glasses_02.jpg</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
+          <t>jacket</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
           <t>hand</t>
         </is>
       </c>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>house</t>
-        </is>
-      </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>lamp</t>
+          <t>glasses</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P89" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="Q89" t="n">
-        <v>0.6</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="R89" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S89" t="n">
         <v>11</v>
       </c>
       <c r="T89" t="n">
+        <v>10</v>
+      </c>
+      <c r="U89" t="n">
         <v>8</v>
       </c>
-      <c r="U89" t="n">
-        <v>9</v>
-      </c>
       <c r="V89" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="W89" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
     </row>
     <row r="90">
@@ -9276,84 +9276,84 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>stimuli/house/house_25.jpg</t>
+          <t>stimuli/hand/hand_30.jpg</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_25.jpg</t>
+          <t>stimuli/bread/bread_49.jpg</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_19.jpg</t>
+          <t>stimuli/lamp/lamp_08.jpg</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_35.jpg</t>
+          <t>stimuli/house/house_05.jpg</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
+          <t>hand</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>bread</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>lamp</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
           <t>house</t>
         </is>
       </c>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t>jacket</t>
-        </is>
-      </c>
-      <c r="K90" t="inlineStr">
-        <is>
-          <t>bicycle</t>
-        </is>
-      </c>
-      <c r="L90" t="inlineStr">
-        <is>
-          <t>chair</t>
-        </is>
-      </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N90" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O90" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P90" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="Q90" t="n">
         <v>0.53</v>
       </c>
-      <c r="Q90" t="n">
-        <v>0.4</v>
-      </c>
       <c r="R90" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S90" t="n">
         <v>12</v>
       </c>
       <c r="T90" t="n">
+        <v>8</v>
+      </c>
+      <c r="U90" t="n">
+        <v>3</v>
+      </c>
+      <c r="V90" t="n">
+        <v>14</v>
+      </c>
+      <c r="W90" t="n">
         <v>9</v>
-      </c>
-      <c r="U90" t="n">
-        <v>10</v>
-      </c>
-      <c r="V90" t="n">
-        <v>2</v>
-      </c>
-      <c r="W90" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="91">
@@ -9375,27 +9375,27 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_25.jpg</t>
+          <t>stimuli/bread/bread_49.jpg</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>stimuli/key/key_14.jpg</t>
+          <t>stimuli/key/key_10.jpg</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_07.jpg</t>
+          <t>stimuli/phone/phone_04.jpg</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_02.jpg</t>
+          <t>stimuli/flower/flower_22.jpg</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -9405,17 +9405,17 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>lamp</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N91" t="inlineStr">
@@ -9425,34 +9425,34 @@
       </c>
       <c r="O91" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P91" t="n">
-        <v>0.73</v>
+        <v>0.8</v>
       </c>
       <c r="Q91" t="n">
-        <v>0.27</v>
+        <v>0.33</v>
       </c>
       <c r="R91" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S91" t="n">
         <v>13</v>
       </c>
       <c r="T91" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="U91" t="n">
         <v>15</v>
       </c>
       <c r="V91" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="W91" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="92">
@@ -9474,22 +9474,22 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>stimuli/key/key_14.jpg</t>
+          <t>stimuli/key/key_10.jpg</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>stimuli/pencil/pencil_25.jpg</t>
+          <t>stimuli/glasses/glasses_02.jpg</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_19.jpg</t>
+          <t>stimuli/bicycle/bicycle_35.jpg</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_06.jpg</t>
+          <t>stimuli/hammer/hammer_26.jpg</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -9499,7 +9499,7 @@
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>pencil</t>
+          <t>glasses</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
@@ -9509,12 +9509,12 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N92" t="inlineStr">
@@ -9524,18 +9524,18 @@
       </c>
       <c r="O92" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P92" t="n">
-        <v>0.67</v>
+        <v>0.73</v>
       </c>
       <c r="Q92" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="R92" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S92" t="n">
@@ -9545,13 +9545,13 @@
         <v>15</v>
       </c>
       <c r="U92" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="V92" t="n">
         <v>2</v>
       </c>
       <c r="W92" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="93">
@@ -9573,52 +9573,52 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>stimuli/pencil/pencil_23.jpg</t>
+          <t>stimuli/lamp/lamp_30.jpg</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>stimuli/guitar/guitar_26.jpg</t>
+          <t>stimuli/car/car_04.jpg</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_13.jpg</t>
+          <t>stimuli/hand/hand_20.jpg</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_44.jpg</t>
+          <t>stimuli/hammer/hammer_09.jpg</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>pencil</t>
+          <t>lamp</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>guitar</t>
+          <t>car</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N93" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O93" t="inlineStr">
@@ -9627,30 +9627,30 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>0.58</v>
+        <v>0.47</v>
       </c>
       <c r="Q93" t="n">
-        <v>0.36</v>
+        <v>0.31</v>
       </c>
       <c r="R93" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S93" t="n">
         <v>2</v>
       </c>
       <c r="T93" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="U93" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="V93" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="W93" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="94">
@@ -9672,42 +9672,42 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>stimuli/guitar/guitar_26.jpg</t>
+          <t>stimuli/car/car_04.jpg</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_01.jpg</t>
+          <t>stimuli/dog/dog_11.jpg</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_30.jpg</t>
+          <t>stimuli/flower/flower_21.jpg</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_22.jpg</t>
+          <t>stimuli/house/house_10.jpg</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>guitar</t>
+          <t>car</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>house</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
@@ -9717,19 +9717,19 @@
       </c>
       <c r="N94" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O94" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P94" t="n">
-        <v>0.8</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="Q94" t="n">
-        <v>0.36</v>
+        <v>0.42</v>
       </c>
       <c r="R94" t="inlineStr">
         <is>
@@ -9740,16 +9740,16 @@
         <v>3</v>
       </c>
       <c r="T94" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="U94" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="V94" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="W94" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="95">
@@ -9771,57 +9771,57 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_01.jpg</t>
+          <t>stimuli/dog/dog_11.jpg</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_30.jpg</t>
+          <t>stimuli/bread/bread_25.jpg</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_39.jpg</t>
+          <t>stimuli/ball/ball_04.jpg</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>stimuli/key/key_13.jpg</t>
+          <t>stimuli/pencil/pencil_15.jpg</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
+          <t>dog</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
           <t>bread</t>
         </is>
       </c>
-      <c r="J95" t="inlineStr">
-        <is>
-          <t>jacket</t>
-        </is>
-      </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>pencil</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N95" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O95" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P95" t="n">
@@ -9832,23 +9832,23 @@
       </c>
       <c r="R95" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S95" t="n">
         <v>4</v>
       </c>
       <c r="T95" t="n">
+        <v>5</v>
+      </c>
+      <c r="U95" t="n">
         <v>3</v>
       </c>
-      <c r="U95" t="n">
-        <v>10</v>
-      </c>
       <c r="V95" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="W95" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="96">
@@ -9870,57 +9870,57 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_30.jpg</t>
+          <t>stimuli/bread/bread_25.jpg</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_10.jpg</t>
+          <t>stimuli/jacket/jacket_06.jpg</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>stimuli/house/house_15.jpg</t>
+          <t>stimuli/hand/hand_20.jpg</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_41.jpg</t>
+          <t>stimuli/phone/phone_22.jpg</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
+          <t>bread</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
           <t>jacket</t>
         </is>
       </c>
-      <c r="J96" t="inlineStr">
+      <c r="K96" t="inlineStr">
         <is>
           <t>hand</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr">
-        <is>
-          <t>house</t>
-        </is>
-      </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>lamp</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N96" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O96" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P96" t="n">
@@ -9931,23 +9931,23 @@
       </c>
       <c r="R96" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S96" t="n">
         <v>5</v>
       </c>
       <c r="T96" t="n">
+        <v>3</v>
+      </c>
+      <c r="U96" t="n">
         <v>10</v>
       </c>
-      <c r="U96" t="n">
+      <c r="V96" t="n">
         <v>8</v>
       </c>
-      <c r="V96" t="n">
-        <v>9</v>
-      </c>
       <c r="W96" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="97">
@@ -9969,27 +9969,27 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_10.jpg</t>
+          <t>stimuli/jacket/jacket_06.jpg</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_03.jpg</t>
+          <t>stimuli/flower/flower_21.jpg</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_04.jpg</t>
+          <t>stimuli/chair/chair_04.jpg</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_22.jpg</t>
+          <t>stimuli/house/house_10.jpg</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -9999,12 +9999,12 @@
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>house</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
@@ -10023,10 +10023,10 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="Q97" t="n">
-        <v>0.53</v>
+        <v>0.58</v>
       </c>
       <c r="R97" t="inlineStr">
         <is>
@@ -10037,16 +10037,16 @@
         <v>6</v>
       </c>
       <c r="T97" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U97" t="n">
         <v>6</v>
       </c>
       <c r="V97" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="W97" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="98">
@@ -10068,22 +10068,22 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_03.jpg</t>
+          <t>stimuli/flower/flower_21.jpg</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_13.jpg</t>
+          <t>stimuli/chair/chair_04.jpg</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>stimuli/pencil/pencil_23.jpg</t>
+          <t>stimuli/bicycle/bicycle_28.jpg</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_01.jpg</t>
+          <t>stimuli/phone/phone_22.jpg</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -10098,12 +10098,12 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>pencil</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
@@ -10113,19 +10113,19 @@
       </c>
       <c r="N98" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O98" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P98" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="Q98" t="n">
-        <v>0.27</v>
+        <v>0.53</v>
       </c>
       <c r="R98" t="inlineStr">
         <is>
@@ -10142,10 +10142,10 @@
         <v>4</v>
       </c>
       <c r="V98" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="W98" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
     </row>
     <row r="99">
@@ -10167,22 +10167,22 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_13.jpg</t>
+          <t>stimuli/chair/chair_04.jpg</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_04.jpg</t>
+          <t>stimuli/bicycle/bicycle_28.jpg</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>stimuli/guitar/guitar_26.jpg</t>
+          <t>stimuli/lamp/lamp_30.jpg</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_10.jpg</t>
+          <t>stimuli/dog/dog_11.jpg</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -10192,27 +10192,27 @@
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>guitar</t>
+          <t>lamp</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N99" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O99" t="inlineStr">
@@ -10221,14 +10221,14 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>0.4</v>
+        <v>0.47</v>
       </c>
       <c r="Q99" t="n">
-        <v>0.2</v>
+        <v>0.33</v>
       </c>
       <c r="R99" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S99" t="n">
@@ -10238,13 +10238,13 @@
         <v>4</v>
       </c>
       <c r="U99" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V99" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="W99" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="100">
@@ -10266,42 +10266,42 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_04.jpg</t>
+          <t>stimuli/bicycle/bicycle_28.jpg</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>stimuli/house/house_15.jpg</t>
+          <t>stimuli/hand/hand_20.jpg</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_30.jpg</t>
+          <t>stimuli/house/house_10.jpg</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_03.jpg</t>
+          <t>stimuli/car/car_04.jpg</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
+          <t>hand</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
           <t>house</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr">
-        <is>
-          <t>jacket</t>
-        </is>
-      </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>car</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
@@ -10320,10 +10320,10 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>0.33</v>
+        <v>0.75</v>
       </c>
       <c r="Q100" t="n">
-        <v>0.2</v>
+        <v>0.47</v>
       </c>
       <c r="R100" t="inlineStr">
         <is>
@@ -10334,16 +10334,16 @@
         <v>9</v>
       </c>
       <c r="T100" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U100" t="n">
+        <v>8</v>
+      </c>
+      <c r="V100" t="n">
         <v>9</v>
       </c>
-      <c r="V100" t="n">
-        <v>10</v>
-      </c>
       <c r="W100" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
     </row>
     <row r="101">
@@ -10365,52 +10365,52 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>stimuli/house/house_15.jpg</t>
+          <t>stimuli/hand/hand_20.jpg</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_39.jpg</t>
+          <t>stimuli/ball/ball_04.jpg</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_44.jpg</t>
+          <t>stimuli/jacket/jacket_06.jpg</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_41.jpg</t>
+          <t>stimuli/chair/chair_04.jpg</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>lamp</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N101" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O101" t="inlineStr">
@@ -10419,30 +10419,30 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>0.8</v>
+        <v>0.33</v>
       </c>
       <c r="Q101" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.2</v>
       </c>
       <c r="R101" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S101" t="n">
         <v>10</v>
       </c>
       <c r="T101" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U101" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="V101" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="W101" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
     </row>
     <row r="102">
@@ -10464,42 +10464,42 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_39.jpg</t>
+          <t>stimuli/ball/ball_04.jpg</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_44.jpg</t>
+          <t>stimuli/house/house_10.jpg</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_22.jpg</t>
+          <t>stimuli/car/car_04.jpg</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>stimuli/key/key_13.jpg</t>
+          <t>stimuli/bread/bread_25.jpg</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>house</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>car</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
@@ -10518,10 +10518,10 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="Q102" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.47</v>
       </c>
       <c r="R102" t="inlineStr">
         <is>
@@ -10532,16 +10532,16 @@
         <v>11</v>
       </c>
       <c r="T102" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="U102" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="V102" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="W102" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
     </row>
     <row r="103">
@@ -10563,27 +10563,27 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_44.jpg</t>
+          <t>stimuli/house/house_10.jpg</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_22.jpg</t>
+          <t>stimuli/hammer/hammer_09.jpg</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>stimuli/guitar/guitar_26.jpg</t>
+          <t>stimuli/lamp/lamp_30.jpg</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_10.jpg</t>
+          <t>stimuli/flower/flower_21.jpg</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>house</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -10593,12 +10593,12 @@
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>guitar</t>
+          <t>lamp</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
@@ -10608,19 +10608,19 @@
       </c>
       <c r="N103" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O103" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P103" t="n">
-        <v>0.67</v>
+        <v>0.73</v>
       </c>
       <c r="Q103" t="n">
-        <v>0.47</v>
+        <v>0.4</v>
       </c>
       <c r="R103" t="inlineStr">
         <is>
@@ -10631,16 +10631,16 @@
         <v>12</v>
       </c>
       <c r="T103" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="U103" t="n">
         <v>7</v>
       </c>
       <c r="V103" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="W103" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="104">
@@ -10662,22 +10662,22 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_22.jpg</t>
+          <t>stimuli/hammer/hammer_09.jpg</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_41.jpg</t>
+          <t>stimuli/phone/phone_22.jpg</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>stimuli/pencil/pencil_23.jpg</t>
+          <t>stimuli/car/car_04.jpg</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>stimuli/house/house_15.jpg</t>
+          <t>stimuli/jacket/jacket_06.jpg</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -10687,27 +10687,27 @@
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>lamp</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>pencil</t>
+          <t>car</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N104" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O104" t="inlineStr">
@@ -10716,14 +10716,14 @@
         </is>
       </c>
       <c r="P104" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="Q104" t="n">
-        <v>0.27</v>
+        <v>0.53</v>
       </c>
       <c r="R104" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S104" t="n">
@@ -10733,13 +10733,13 @@
         <v>7</v>
       </c>
       <c r="U104" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="V104" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="W104" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="105">
@@ -10761,47 +10761,47 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_41.jpg</t>
+          <t>stimuli/phone/phone_22.jpg</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>stimuli/key/key_13.jpg</t>
+          <t>stimuli/pencil/pencil_15.jpg</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_01.jpg</t>
+          <t>stimuli/dog/dog_11.jpg</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_04.jpg</t>
+          <t>stimuli/chair/chair_04.jpg</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>lamp</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>pencil</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N105" t="inlineStr">
@@ -10811,34 +10811,34 @@
       </c>
       <c r="O105" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P105" t="n">
         <v>0.73</v>
       </c>
       <c r="Q105" t="n">
-        <v>0.4</v>
+        <v>0.47</v>
       </c>
       <c r="R105" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S105" t="n">
         <v>14</v>
       </c>
       <c r="T105" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="U105" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="V105" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="W105" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/psychopy_exp_files/sequences/learning_block2_fixed-middle-10_27.xlsx
+++ b/psychopy_exp_files/sequences/learning_block2_fixed-middle-10_27.xlsx
@@ -574,12 +574,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_28.jpg</t>
+          <t>stimuli/chair/chair_04.jpg</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_09.jpg</t>
+          <t>stimuli/house/house_10.jpg</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -594,38 +594,38 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>house</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>0.53</v>
+        <v>0.58</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.31</v>
+        <v>0.36</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S2" t="n">
@@ -638,10 +638,10 @@
         <v>11</v>
       </c>
       <c r="V2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="W2" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3">
@@ -673,12 +673,12 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>stimuli/house/house_10.jpg</t>
+          <t>stimuli/jacket/jacket_06.jpg</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>stimuli/phone/phone_22.jpg</t>
+          <t>stimuli/pencil/pencil_15.jpg</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -693,17 +693,17 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>pencil</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -713,18 +713,18 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>0.42</v>
+        <v>0.75</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.31</v>
+        <v>0.25</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S3" t="n">
@@ -737,10 +737,10 @@
         <v>5</v>
       </c>
       <c r="V3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W3" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4">
@@ -772,12 +772,12 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_20.jpg</t>
+          <t>stimuli/phone/phone_22.jpg</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>stimuli/pencil/pencil_15.jpg</t>
+          <t>stimuli/lamp/lamp_30.jpg</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -792,12 +792,12 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>pencil</t>
+          <t>lamp</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -807,19 +807,19 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>0.58</v>
+        <v>0.36</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.31</v>
+        <v>0.2</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
@@ -836,10 +836,10 @@
         <v>3</v>
       </c>
       <c r="V4" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="W4" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5">
@@ -871,12 +871,12 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_21.jpg</t>
+          <t>stimuli/bicycle/bicycle_28.jpg</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_04.jpg</t>
+          <t>stimuli/hammer/hammer_09.jpg</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -891,38 +891,38 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>0.8</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.58</v>
+        <v>0.47</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S5" t="n">
@@ -935,10 +935,10 @@
         <v>10</v>
       </c>
       <c r="V5" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="W5" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6">
@@ -975,7 +975,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_09.jpg</t>
+          <t>stimuli/ball/ball_04.jpg</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -995,17 +995,17 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -1017,11 +1017,11 @@
         <v>0.8</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.53</v>
+        <v>0.64</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S6" t="n">
@@ -1037,7 +1037,7 @@
         <v>4</v>
       </c>
       <c r="W6" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -1069,12 +1069,12 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_30.jpg</t>
+          <t>stimuli/hand/hand_20.jpg</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_25.jpg</t>
+          <t>stimuli/pencil/pencil_15.jpg</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1089,17 +1089,17 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>lamp</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>pencil</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1109,18 +1109,18 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>0.4</v>
+        <v>0.75</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.2</v>
+        <v>0.47</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S7" t="n">
@@ -1133,10 +1133,10 @@
         <v>4</v>
       </c>
       <c r="V7" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="W7" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8">
@@ -1168,12 +1168,12 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>stimuli/house/house_10.jpg</t>
+          <t>stimuli/dog/dog_11.jpg</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>stimuli/car/car_04.jpg</t>
+          <t>stimuli/jacket/jacket_06.jpg</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1188,38 +1188,38 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>car</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.33</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S8" t="n">
@@ -1232,10 +1232,10 @@
         <v>2</v>
       </c>
       <c r="V8" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="W8" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_06.jpg</t>
+          <t>stimuli/bread/bread_25.jpg</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1292,33 +1292,33 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P9" t="n">
         <v>0.53</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.27</v>
+        <v>0.33</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S9" t="n">
@@ -1334,7 +1334,7 @@
         <v>14</v>
       </c>
       <c r="W9" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -1366,12 +1366,12 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_09.jpg</t>
+          <t>stimuli/car/car_04.jpg</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_11.jpg</t>
+          <t>stimuli/flower/flower_21.jpg</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1386,38 +1386,38 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>car</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>0.75</v>
+        <v>0.53</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.47</v>
+        <v>0.27</v>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S10" t="n">
@@ -1430,10 +1430,10 @@
         <v>1</v>
       </c>
       <c r="V10" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="W10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_25.jpg</t>
+          <t>stimuli/hammer/hammer_09.jpg</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_21.jpg</t>
+          <t>stimuli/pencil/pencil_15.jpg</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1485,38 +1485,38 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>pencil</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>0.47</v>
+        <v>0.8</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.33</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S11" t="n">
@@ -1529,10 +1529,10 @@
         <v>9</v>
       </c>
       <c r="V11" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="W11" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
     </row>
     <row r="12">
@@ -1569,7 +1569,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_04.jpg</t>
+          <t>stimuli/jacket/jacket_06.jpg</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1611,7 +1611,7 @@
         <v>0.73</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.33</v>
+        <v>0.47</v>
       </c>
       <c r="R12" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         <v>14</v>
       </c>
       <c r="W12" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13">
@@ -1693,17 +1693,17 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P13" t="n">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S13" t="n">
@@ -1762,7 +1762,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_28.jpg</t>
+          <t>stimuli/flower/flower_21.jpg</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1792,28 +1792,28 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>0.4</v>
+        <v>0.53</v>
       </c>
       <c r="Q14" t="n">
         <v>0.26</v>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S14" t="n">
@@ -1826,7 +1826,7 @@
         <v>16</v>
       </c>
       <c r="V14" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="W14" t="n">
         <v>14</v>
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_30.jpg</t>
+          <t>stimuli/chair/chair_16.jpg</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1881,7 +1881,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1896,16 +1896,16 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="Q15" t="n">
         <v>0.31</v>
@@ -1925,7 +1925,7 @@
         <v>14</v>
       </c>
       <c r="V15" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="W15" t="n">
         <v>3</v>
@@ -1960,12 +1960,12 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_23.jpg</t>
+          <t>stimuli/hand/hand_30.jpg</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>stimuli/key/key_10.jpg</t>
+          <t>stimuli/glasses/glasses_02.jpg</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1980,38 +1980,38 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>glasses</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>0.64</v>
+        <v>0.42</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.31</v>
+        <v>0.25</v>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S16" t="n">
@@ -2024,10 +2024,10 @@
         <v>2</v>
       </c>
       <c r="V16" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="W16" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="17">
@@ -2064,7 +2064,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>stimuli/glasses/glasses_02.jpg</t>
+          <t>stimuli/key/key_10.jpg</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>glasses</t>
+          <t>key</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -2094,19 +2094,19 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P17" t="n">
         <v>0.75</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.31</v>
+        <v>0.36</v>
       </c>
       <c r="R17" t="inlineStr">
         <is>
@@ -2126,7 +2126,7 @@
         <v>4</v>
       </c>
       <c r="W17" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="18">
@@ -2158,12 +2158,12 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_22.jpg</t>
+          <t>stimuli/jacket/jacket_35.jpg</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_30.jpg</t>
+          <t>stimuli/glasses/glasses_02.jpg</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2178,38 +2178,38 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>glasses</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.58</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.53</v>
+        <v>0.36</v>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S18" t="n">
@@ -2222,10 +2222,10 @@
         <v>5</v>
       </c>
       <c r="V18" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="W18" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
     </row>
     <row r="19">
@@ -2356,12 +2356,12 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_26.jpg</t>
+          <t>stimuli/flower/flower_22.jpg</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>stimuli/glasses/glasses_02.jpg</t>
+          <t>stimuli/key/key_10.jpg</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2376,38 +2376,38 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>glasses</t>
+          <t>key</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.47</v>
+        <v>0.53</v>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S20" t="n">
@@ -2420,10 +2420,10 @@
         <v>1</v>
       </c>
       <c r="V20" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W20" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="21">
@@ -2455,12 +2455,12 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>stimuli/key/key_10.jpg</t>
+          <t>stimuli/hammer/hammer_26.jpg</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_08.jpg</t>
+          <t>stimuli/glasses/glasses_02.jpg</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2475,38 +2475,38 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>lamp</t>
+          <t>glasses</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P21" t="n">
-        <v>0.58</v>
+        <v>0.8</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.4</v>
+        <v>0.53</v>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S21" t="n">
@@ -2519,10 +2519,10 @@
         <v>6</v>
       </c>
       <c r="V21" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="W21" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
     </row>
     <row r="22">
@@ -2554,12 +2554,12 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_08.jpg</t>
+          <t>stimuli/bicycle/bicycle_35.jpg</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>stimuli/house/house_05.jpg</t>
+          <t>stimuli/dog/dog_30.jpg</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2574,22 +2574,22 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>lamp</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -2598,14 +2598,14 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>0.47</v>
+        <v>0.4</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.33</v>
+        <v>0.27</v>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S22" t="n">
@@ -2618,10 +2618,10 @@
         <v>7</v>
       </c>
       <c r="V22" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="W22" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23">
@@ -2653,12 +2653,12 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_30.jpg</t>
+          <t>stimuli/glasses/glasses_02.jpg</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>stimuli/glasses/glasses_02.jpg</t>
+          <t>stimuli/house/house_05.jpg</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2673,38 +2673,38 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>glasses</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>glasses</t>
+          <t>house</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P23" t="n">
-        <v>0.8</v>
+        <v>0.64</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.64</v>
+        <v>0.4</v>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S23" t="n">
@@ -2717,10 +2717,10 @@
         <v>10</v>
       </c>
       <c r="V23" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="W23" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
     </row>
     <row r="24">
@@ -2757,7 +2757,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_23.jpg</t>
+          <t>stimuli/flower/flower_22.jpg</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2777,12 +2777,12 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -2792,18 +2792,18 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P24" t="n">
         <v>0.6</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.27</v>
+        <v>0.2</v>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S24" t="n">
@@ -2819,7 +2819,7 @@
         <v>14</v>
       </c>
       <c r="W24" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="25">
@@ -2851,12 +2851,12 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>stimuli/house/house_05.jpg</t>
+          <t>stimuli/phone/phone_04.jpg</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_26.jpg</t>
+          <t>stimuli/ball/ball_23.jpg</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2871,17 +2871,17 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -2891,18 +2891,18 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P25" t="n">
-        <v>0.53</v>
+        <v>0.73</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.2</v>
+        <v>0.33</v>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S25" t="n">
@@ -2915,10 +2915,10 @@
         <v>3</v>
       </c>
       <c r="V25" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="W25" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -2950,12 +2950,12 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>stimuli/phone/phone_04.jpg</t>
+          <t>stimuli/bicycle/bicycle_35.jpg</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_35.jpg</t>
+          <t>stimuli/dog/dog_30.jpg</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2970,17 +2970,17 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -2990,18 +2990,18 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P26" t="n">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.2</v>
+        <v>0.53</v>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S26" t="n">
@@ -3014,10 +3014,10 @@
         <v>15</v>
       </c>
       <c r="V26" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="W26" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="27">
@@ -3054,7 +3054,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_22.jpg</t>
+          <t>stimuli/ball/ball_23.jpg</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -3089,18 +3089,18 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P27" t="n">
         <v>0.8</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.4</v>
+        <v>0.47</v>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S27" t="n">
@@ -3116,7 +3116,7 @@
         <v>14</v>
       </c>
       <c r="W27" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -3148,12 +3148,12 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_20.jpg</t>
+          <t>stimuli/bread/bread_25.jpg</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>stimuli/phone/phone_22.jpg</t>
+          <t>stimuli/pencil/pencil_15.jpg</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>pencil</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -3192,10 +3192,10 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>0.47</v>
+        <v>0.75</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="R28" t="inlineStr">
         <is>
@@ -3212,10 +3212,10 @@
         <v>11</v>
       </c>
       <c r="V28" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="W28" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="29">
@@ -3252,7 +3252,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>stimuli/pencil/pencil_15.jpg</t>
+          <t>stimuli/phone/phone_22.jpg</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3272,17 +3272,17 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>pencil</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
@@ -3294,11 +3294,11 @@
         <v>0.42</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.25</v>
+        <v>0.31</v>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S29" t="n">
@@ -3314,7 +3314,7 @@
         <v>9</v>
       </c>
       <c r="W29" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="30">
@@ -3346,12 +3346,12 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_06.jpg</t>
+          <t>stimuli/chair/chair_04.jpg</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_30.jpg</t>
+          <t>stimuli/pencil/pencil_15.jpg</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3366,22 +3366,22 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>lamp</t>
+          <t>pencil</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
@@ -3390,14 +3390,14 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>0.8</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.2</v>
+        <v>0.31</v>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S30" t="n">
@@ -3410,10 +3410,10 @@
         <v>3</v>
       </c>
       <c r="V30" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="W30" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="31">
@@ -3445,12 +3445,12 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_20.jpg</t>
+          <t>stimuli/bicycle/bicycle_28.jpg</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_09.jpg</t>
+          <t>stimuli/lamp/lamp_30.jpg</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3465,38 +3465,38 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>lamp</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P31" t="n">
-        <v>0.64</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.47</v>
+        <v>0.27</v>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S31" t="n">
@@ -3509,10 +3509,10 @@
         <v>10</v>
       </c>
       <c r="V31" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="W31" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
     </row>
     <row r="32">
@@ -3544,12 +3544,12 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_04.jpg</t>
+          <t>stimuli/hammer/hammer_09.jpg</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>stimuli/phone/phone_22.jpg</t>
+          <t>stimuli/pencil/pencil_15.jpg</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -3564,38 +3564,38 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>pencil</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P32" t="n">
-        <v>0.8</v>
+        <v>0.53</v>
       </c>
       <c r="Q32" t="n">
-        <v>0.47</v>
+        <v>0.42</v>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S32" t="n">
@@ -3608,10 +3608,10 @@
         <v>6</v>
       </c>
       <c r="V32" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="W32" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="33">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_04.jpg</t>
+          <t>stimuli/lamp/lamp_30.jpg</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>stimuli/pencil/pencil_15.jpg</t>
+          <t>stimuli/dog/dog_11.jpg</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -3663,17 +3663,17 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>lamp</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>pencil</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -3683,18 +3683,18 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P33" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.4</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.47</v>
+        <v>0.27</v>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S33" t="n">
@@ -3707,10 +3707,10 @@
         <v>4</v>
       </c>
       <c r="V33" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="W33" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="34">
@@ -3742,14 +3742,14 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
+          <t>stimuli/ball/ball_04.jpg</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
           <t>stimuli/phone/phone_22.jpg</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>stimuli/car/car_04.jpg</t>
-        </is>
-      </c>
       <c r="I34" t="inlineStr">
         <is>
           <t>chair</t>
@@ -3762,38 +3762,38 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
+          <t>ball</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
           <t>phone</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>car</t>
-        </is>
-      </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P34" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="Q34" t="n">
         <v>0.58</v>
       </c>
-      <c r="Q34" t="n">
-        <v>0.4</v>
-      </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S34" t="n">
@@ -3806,10 +3806,10 @@
         <v>2</v>
       </c>
       <c r="V34" t="n">
+        <v>1</v>
+      </c>
+      <c r="W34" t="n">
         <v>17</v>
-      </c>
-      <c r="W34" t="n">
-        <v>11</v>
       </c>
     </row>
     <row r="35">
@@ -3841,12 +3841,12 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_09.jpg</t>
+          <t>stimuli/dog/dog_11.jpg</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_25.jpg</t>
+          <t>stimuli/flower/flower_21.jpg</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -3861,38 +3861,38 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P35" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.4</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.33</v>
+        <v>0.2</v>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S35" t="n">
@@ -3905,10 +3905,10 @@
         <v>8</v>
       </c>
       <c r="V35" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="W35" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="36">
@@ -3940,12 +3940,12 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_30.jpg</t>
+          <t>stimuli/pencil/pencil_15.jpg</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_11.jpg</t>
+          <t>stimuli/car/car_04.jpg</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -3960,38 +3960,38 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>lamp</t>
+          <t>pencil</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>car</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P36" t="n">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.47</v>
+        <v>0.53</v>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S36" t="n">
@@ -4004,10 +4004,10 @@
         <v>1</v>
       </c>
       <c r="V36" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="W36" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="37">
@@ -4039,12 +4039,12 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>stimuli/car/car_04.jpg</t>
+          <t>stimuli/lamp/lamp_30.jpg</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_28.jpg</t>
+          <t>stimuli/jacket/jacket_06.jpg</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -4059,38 +4059,38 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>car</t>
+          <t>lamp</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P37" t="n">
-        <v>0.6</v>
+        <v>0.67</v>
       </c>
       <c r="Q37" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S37" t="n">
@@ -4103,10 +4103,10 @@
         <v>9</v>
       </c>
       <c r="V37" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="W37" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="38">
@@ -4138,12 +4138,12 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_30.jpg</t>
+          <t>stimuli/pencil/pencil_15.jpg</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_21.jpg</t>
+          <t>stimuli/hand/hand_20.jpg</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -4158,12 +4158,12 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>lamp</t>
+          <t>pencil</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -4182,10 +4182,10 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="Q38" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="R38" t="inlineStr">
         <is>
@@ -4202,10 +4202,10 @@
         <v>7</v>
       </c>
       <c r="V38" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="W38" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="39">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_11.jpg</t>
+          <t>stimuli/lamp/lamp_30.jpg</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_20.jpg</t>
+          <t>stimuli/jacket/jacket_06.jpg</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -4257,22 +4257,22 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>lamp</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
@@ -4281,14 +4281,14 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>0.67</v>
+        <v>0.8</v>
       </c>
       <c r="Q39" t="n">
-        <v>0.27</v>
+        <v>0.53</v>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S39" t="n">
@@ -4301,10 +4301,10 @@
         <v>17</v>
       </c>
       <c r="V39" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="W39" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="40">
@@ -4336,12 +4336,12 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_04.jpg</t>
+          <t>stimuli/car/car_04.jpg</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_30.jpg</t>
+          <t>stimuli/bread/bread_25.jpg</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -4356,12 +4356,12 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>car</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>lamp</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -4371,19 +4371,19 @@
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P40" t="n">
-        <v>0.47</v>
+        <v>0.8</v>
       </c>
       <c r="Q40" t="n">
-        <v>0.26</v>
+        <v>0.67</v>
       </c>
       <c r="R40" t="inlineStr">
         <is>
@@ -4400,10 +4400,10 @@
         <v>16</v>
       </c>
       <c r="V40" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="W40" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
     </row>
     <row r="41">
@@ -4435,7 +4435,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_22.jpg</t>
+          <t>stimuli/bicycle/bicycle_35.jpg</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -4455,7 +4455,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -4465,28 +4465,28 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P41" t="n">
-        <v>0.53</v>
+        <v>0.8</v>
       </c>
       <c r="Q41" t="n">
         <v>0.25</v>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S41" t="n">
@@ -4499,7 +4499,7 @@
         <v>14</v>
       </c>
       <c r="V41" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="W41" t="n">
         <v>15</v>
@@ -4564,12 +4564,12 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
@@ -4585,7 +4585,7 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S42" t="n">
@@ -4633,7 +4633,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_35.jpg</t>
+          <t>stimuli/hammer/hammer_26.jpg</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -4653,7 +4653,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -4663,7 +4663,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -4673,18 +4673,18 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P43" t="n">
-        <v>0.53</v>
+        <v>0.58</v>
       </c>
       <c r="Q43" t="n">
         <v>0.42</v>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S43" t="n">
@@ -4697,7 +4697,7 @@
         <v>9</v>
       </c>
       <c r="V43" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="W43" t="n">
         <v>3</v>
@@ -4732,12 +4732,12 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_26.jpg</t>
+          <t>stimuli/hand/hand_30.jpg</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>stimuli/key/key_10.jpg</t>
+          <t>stimuli/glasses/glasses_02.jpg</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -4752,12 +4752,12 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>glasses</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -4767,19 +4767,19 @@
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P44" t="n">
-        <v>0.64</v>
+        <v>0.53</v>
       </c>
       <c r="Q44" t="n">
-        <v>0.42</v>
+        <v>0.36</v>
       </c>
       <c r="R44" t="inlineStr">
         <is>
@@ -4796,10 +4796,10 @@
         <v>5</v>
       </c>
       <c r="V44" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W44" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="45">
@@ -4831,12 +4831,12 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_30.jpg</t>
+          <t>stimuli/ball/ball_23.jpg</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>stimuli/glasses/glasses_02.jpg</t>
+          <t>stimuli/key/key_10.jpg</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -4851,17 +4851,17 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>glasses</t>
+          <t>key</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -4871,18 +4871,18 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P45" t="n">
-        <v>0.58</v>
+        <v>0.8</v>
       </c>
       <c r="Q45" t="n">
-        <v>0.42</v>
+        <v>0.47</v>
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S45" t="n">
@@ -4895,10 +4895,10 @@
         <v>4</v>
       </c>
       <c r="V45" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="W45" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="46">
@@ -4930,12 +4930,12 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_26.jpg</t>
+          <t>stimuli/flower/flower_22.jpg</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_08.jpg</t>
+          <t>stimuli/bread/bread_49.jpg</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -4950,12 +4950,12 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>lamp</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -4974,10 +4974,10 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="Q46" t="n">
-        <v>0.33</v>
+        <v>0.58</v>
       </c>
       <c r="R46" t="inlineStr">
         <is>
@@ -4994,10 +4994,10 @@
         <v>1</v>
       </c>
       <c r="V46" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W46" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
     </row>
     <row r="47">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>stimuli/glasses/glasses_02.jpg</t>
+          <t>stimuli/key/key_10.jpg</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_30.jpg</t>
+          <t>stimuli/lamp/lamp_08.jpg</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -5049,12 +5049,12 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>glasses</t>
+          <t>key</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>lamp</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -5064,19 +5064,19 @@
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P47" t="n">
-        <v>0.53</v>
+        <v>0.58</v>
       </c>
       <c r="Q47" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="R47" t="inlineStr">
         <is>
@@ -5093,10 +5093,10 @@
         <v>6</v>
       </c>
       <c r="V47" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="W47" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="48">
@@ -5128,14 +5128,14 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
+          <t>stimuli/phone/phone_04.jpg</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
           <t>stimuli/house/house_05.jpg</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>stimuli/chair/chair_16.jpg</t>
-        </is>
-      </c>
       <c r="I48" t="inlineStr">
         <is>
           <t>flower</t>
@@ -5148,38 +5148,38 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
+          <t>phone</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
           <t>house</t>
         </is>
       </c>
-      <c r="L48" t="inlineStr">
-        <is>
-          <t>chair</t>
-        </is>
-      </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P48" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="Q48" t="n">
         <v>0.33</v>
       </c>
-      <c r="Q48" t="n">
-        <v>0.2</v>
-      </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S48" t="n">
@@ -5192,10 +5192,10 @@
         <v>7</v>
       </c>
       <c r="V48" t="n">
+        <v>17</v>
+      </c>
+      <c r="W48" t="n">
         <v>9</v>
-      </c>
-      <c r="W48" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="49">
@@ -5227,12 +5227,12 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>stimuli/phone/phone_04.jpg</t>
+          <t>stimuli/hand/hand_30.jpg</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>stimuli/house/house_05.jpg</t>
+          <t>stimuli/dog/dog_30.jpg</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -5247,38 +5247,38 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P49" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="Q49" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S49" t="n">
@@ -5291,10 +5291,10 @@
         <v>10</v>
       </c>
       <c r="V49" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="W49" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="50">
@@ -5326,12 +5326,12 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_49.jpg</t>
+          <t>stimuli/phone/phone_04.jpg</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_35.jpg</t>
+          <t>stimuli/chair/chair_16.jpg</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -5346,38 +5346,38 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P50" t="n">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="Q50" t="n">
-        <v>0.53</v>
+        <v>0.33</v>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S50" t="n">
@@ -5390,10 +5390,10 @@
         <v>8</v>
       </c>
       <c r="V50" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="W50" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="51">
@@ -5425,12 +5425,12 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_08.jpg</t>
+          <t>stimuli/bicycle/bicycle_35.jpg</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_23.jpg</t>
+          <t>stimuli/flower/flower_22.jpg</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -5445,38 +5445,38 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>lamp</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P51" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="Q51" t="n">
-        <v>0.33</v>
+        <v>0.27</v>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S51" t="n">
@@ -5489,10 +5489,10 @@
         <v>3</v>
       </c>
       <c r="V51" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="W51" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="52">
@@ -5524,12 +5524,12 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>stimuli/phone/phone_04.jpg</t>
+          <t>stimuli/house/house_05.jpg</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_26.jpg</t>
+          <t>stimuli/jacket/jacket_35.jpg</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -5544,38 +5544,38 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>house</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P52" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="Q52" t="n">
-        <v>0.27</v>
+        <v>0.2</v>
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S52" t="n">
@@ -5588,10 +5588,10 @@
         <v>15</v>
       </c>
       <c r="V52" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="W52" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="53">
@@ -5628,7 +5628,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_23.jpg</t>
+          <t>stimuli/dog/dog_30.jpg</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -5648,17 +5648,17 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
@@ -5670,11 +5670,11 @@
         <v>0.8</v>
       </c>
       <c r="Q53" t="n">
-        <v>0.47</v>
+        <v>0.6</v>
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S53" t="n">
@@ -5690,7 +5690,7 @@
         <v>14</v>
       </c>
       <c r="W53" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="54">
@@ -5722,12 +5722,12 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_11.jpg</t>
+          <t>stimuli/jacket/jacket_06.jpg</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_09.jpg</t>
+          <t>stimuli/phone/phone_22.jpg</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -5742,17 +5742,17 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -5762,18 +5762,18 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P54" t="n">
-        <v>0.8</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="Q54" t="n">
-        <v>0.31</v>
+        <v>0.25</v>
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S54" t="n">
@@ -5786,10 +5786,10 @@
         <v>11</v>
       </c>
       <c r="V54" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="W54" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
     </row>
     <row r="55">
@@ -5821,7 +5821,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_06.jpg</t>
+          <t>stimuli/bicycle/bicycle_28.jpg</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -5841,7 +5841,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -5851,7 +5851,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -5861,18 +5861,18 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P55" t="n">
-        <v>0.75</v>
+        <v>0.58</v>
       </c>
       <c r="Q55" t="n">
         <v>0.25</v>
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S55" t="n">
@@ -5885,7 +5885,7 @@
         <v>5</v>
       </c>
       <c r="V55" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="W55" t="n">
         <v>16</v>
@@ -5955,12 +5955,12 @@
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P56" t="n">
@@ -6019,7 +6019,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_28.jpg</t>
+          <t>stimuli/hand/hand_20.jpg</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -6039,7 +6039,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -6049,7 +6049,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -6059,18 +6059,18 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P57" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="Q57" t="n">
         <v>0.42</v>
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S57" t="n">
@@ -6083,7 +6083,7 @@
         <v>10</v>
       </c>
       <c r="V57" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="W57" t="n">
         <v>17</v>
@@ -6148,7 +6148,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -6158,7 +6158,7 @@
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P58" t="n">
@@ -6169,7 +6169,7 @@
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S58" t="n">
@@ -6217,12 +6217,12 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_20.jpg</t>
+          <t>stimuli/ball/ball_04.jpg</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>stimuli/house/house_10.jpg</t>
+          <t>stimuli/phone/phone_22.jpg</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -6237,12 +6237,12 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
@@ -6252,19 +6252,19 @@
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P59" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="Q59" t="n">
-        <v>0.64</v>
+        <v>0.53</v>
       </c>
       <c r="R59" t="inlineStr">
         <is>
@@ -6281,10 +6281,10 @@
         <v>4</v>
       </c>
       <c r="V59" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="W59" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
     </row>
     <row r="60">
@@ -6316,12 +6316,12 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_04.jpg</t>
+          <t>stimuli/dog/dog_11.jpg</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_09.jpg</t>
+          <t>stimuli/jacket/jacket_06.jpg</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -6336,12 +6336,12 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
@@ -6351,19 +6351,19 @@
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P60" t="n">
-        <v>0.75</v>
+        <v>0.33</v>
       </c>
       <c r="Q60" t="n">
-        <v>0.64</v>
+        <v>0.2</v>
       </c>
       <c r="R60" t="inlineStr">
         <is>
@@ -6380,10 +6380,10 @@
         <v>2</v>
       </c>
       <c r="V60" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="W60" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="61">
@@ -6415,7 +6415,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_25.jpg</t>
+          <t>stimuli/lamp/lamp_30.jpg</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -6435,7 +6435,7 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>lamp</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -6445,28 +6445,28 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P61" t="n">
-        <v>0.33</v>
+        <v>0.53</v>
       </c>
       <c r="Q61" t="n">
         <v>0.2</v>
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S61" t="n">
@@ -6479,7 +6479,7 @@
         <v>8</v>
       </c>
       <c r="V61" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="W61" t="n">
         <v>6</v>
@@ -6514,12 +6514,12 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_30.jpg</t>
+          <t>stimuli/house/house_10.jpg</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_11.jpg</t>
+          <t>stimuli/phone/phone_22.jpg</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -6534,38 +6534,38 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>lamp</t>
+          <t>house</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P62" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="Q62" t="n">
-        <v>0.47</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S62" t="n">
@@ -6578,10 +6578,10 @@
         <v>1</v>
       </c>
       <c r="V62" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="W62" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
     </row>
     <row r="63">
@@ -6613,12 +6613,12 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>stimuli/car/car_04.jpg</t>
+          <t>stimuli/lamp/lamp_30.jpg</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_21.jpg</t>
+          <t>stimuli/bread/bread_25.jpg</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -6633,17 +6633,17 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>car</t>
+          <t>lamp</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -6653,18 +6653,18 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P63" t="n">
-        <v>0.6</v>
+        <v>0.67</v>
       </c>
       <c r="Q63" t="n">
-        <v>0.33</v>
+        <v>0.47</v>
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S63" t="n">
@@ -6677,10 +6677,10 @@
         <v>9</v>
       </c>
       <c r="V63" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="W63" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="64">
@@ -6712,7 +6712,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_04.jpg</t>
+          <t>stimuli/car/car_04.jpg</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -6732,7 +6732,7 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>car</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -6742,12 +6742,12 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
@@ -6756,14 +6756,14 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>0.33</v>
+        <v>0.67</v>
       </c>
       <c r="Q64" t="n">
         <v>0.2</v>
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S64" t="n">
@@ -6776,7 +6776,7 @@
         <v>7</v>
       </c>
       <c r="V64" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="W64" t="n">
         <v>8</v>
@@ -6811,7 +6811,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_06.jpg</t>
+          <t>stimuli/bread/bread_25.jpg</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -6831,7 +6831,7 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -6846,16 +6846,16 @@
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P65" t="n">
-        <v>0.53</v>
+        <v>0.6</v>
       </c>
       <c r="Q65" t="n">
         <v>0.33</v>
@@ -6875,7 +6875,7 @@
         <v>17</v>
       </c>
       <c r="V65" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="W65" t="n">
         <v>2</v>
@@ -6910,12 +6910,12 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_11.jpg</t>
+          <t>stimuli/flower/flower_21.jpg</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_04.jpg</t>
+          <t>stimuli/lamp/lamp_30.jpg</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -6930,22 +6930,22 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>lamp</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
@@ -6954,14 +6954,14 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>0.73</v>
+        <v>0.53</v>
       </c>
       <c r="Q66" t="n">
-        <v>0.27</v>
+        <v>0.26</v>
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S66" t="n">
@@ -6974,10 +6974,10 @@
         <v>16</v>
       </c>
       <c r="V66" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W66" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
     </row>
     <row r="67">
@@ -7009,7 +7009,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_35.jpg</t>
+          <t>stimuli/ball/ball_23.jpg</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -7029,7 +7029,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -7039,7 +7039,7 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
@@ -7049,18 +7049,18 @@
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P67" t="n">
-        <v>0.42</v>
+        <v>0.58</v>
       </c>
       <c r="Q67" t="n">
         <v>0.2</v>
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S67" t="n">
@@ -7073,7 +7073,7 @@
         <v>14</v>
       </c>
       <c r="V67" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="W67" t="n">
         <v>18</v>
@@ -7108,12 +7108,12 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_26.jpg</t>
+          <t>stimuli/dog/dog_30.jpg</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_49.jpg</t>
+          <t>stimuli/key/key_10.jpg</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -7128,17 +7128,17 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>key</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
@@ -7148,18 +7148,18 @@
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P68" t="n">
-        <v>0.53</v>
+        <v>0.75</v>
       </c>
       <c r="Q68" t="n">
-        <v>0.36</v>
+        <v>0.31</v>
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S68" t="n">
@@ -7172,10 +7172,10 @@
         <v>2</v>
       </c>
       <c r="V68" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="W68" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
     </row>
     <row r="69">
@@ -7207,14 +7207,14 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
+          <t>stimuli/flower/flower_22.jpg</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
           <t>stimuli/hand/hand_30.jpg</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>stimuli/key/key_10.jpg</t>
-        </is>
-      </c>
       <c r="I69" t="inlineStr">
         <is>
           <t>bicycle</t>
@@ -7227,22 +7227,22 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
+          <t>flower</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
           <t>hand</t>
         </is>
       </c>
-      <c r="L69" t="inlineStr">
-        <is>
-          <t>key</t>
-        </is>
-      </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
@@ -7251,14 +7251,14 @@
         </is>
       </c>
       <c r="P69" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="Q69" t="n">
         <v>0.47</v>
       </c>
-      <c r="Q69" t="n">
-        <v>0.36</v>
-      </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S69" t="n">
@@ -7271,10 +7271,10 @@
         <v>9</v>
       </c>
       <c r="V69" t="n">
+        <v>6</v>
+      </c>
+      <c r="W69" t="n">
         <v>8</v>
-      </c>
-      <c r="W69" t="n">
-        <v>15</v>
       </c>
     </row>
     <row r="70">
@@ -7306,12 +7306,12 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_16.jpg</t>
+          <t>stimuli/jacket/jacket_35.jpg</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>stimuli/phone/phone_04.jpg</t>
+          <t>stimuli/bread/bread_49.jpg</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -7326,12 +7326,12 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
@@ -7341,19 +7341,19 @@
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P70" t="n">
-        <v>0.8</v>
+        <v>0.58</v>
       </c>
       <c r="Q70" t="n">
-        <v>0.27</v>
+        <v>0.47</v>
       </c>
       <c r="R70" t="inlineStr">
         <is>
@@ -7370,10 +7370,10 @@
         <v>5</v>
       </c>
       <c r="V70" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="W70" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
     </row>
     <row r="71">
@@ -7405,12 +7405,12 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_23.jpg</t>
+          <t>stimuli/hammer/hammer_26.jpg</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_35.jpg</t>
+          <t>stimuli/key/key_10.jpg</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>key</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
@@ -7440,19 +7440,19 @@
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P71" t="n">
-        <v>0.8</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="Q71" t="n">
-        <v>0.64</v>
+        <v>0.47</v>
       </c>
       <c r="R71" t="inlineStr">
         <is>
@@ -7469,10 +7469,10 @@
         <v>4</v>
       </c>
       <c r="V71" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="W71" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="72">
@@ -7504,12 +7504,12 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_22.jpg</t>
+          <t>stimuli/phone/phone_04.jpg</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_49.jpg</t>
+          <t>stimuli/bicycle/bicycle_35.jpg</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -7524,38 +7524,38 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P72" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="Q72" t="n">
-        <v>0.58</v>
+        <v>0.27</v>
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S72" t="n">
@@ -7568,10 +7568,10 @@
         <v>1</v>
       </c>
       <c r="V72" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="W72" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="73">
@@ -7603,7 +7603,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>stimuli/phone/phone_04.jpg</t>
+          <t>stimuli/glasses/glasses_02.jpg</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -7623,7 +7623,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>glasses</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -7647,7 +7647,7 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>0.47</v>
+        <v>0.53</v>
       </c>
       <c r="Q73" t="n">
         <v>0.27</v>
@@ -7667,7 +7667,7 @@
         <v>6</v>
       </c>
       <c r="V73" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="W73" t="n">
         <v>9</v>
@@ -7702,12 +7702,12 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>stimuli/glasses/glasses_02.jpg</t>
+          <t>stimuli/bread/bread_49.jpg</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_35.jpg</t>
+          <t>stimuli/lamp/lamp_08.jpg</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -7722,38 +7722,38 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>glasses</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>lamp</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P74" t="n">
-        <v>0.58</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="Q74" t="n">
-        <v>0.4</v>
+        <v>0.47</v>
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S74" t="n">
@@ -7766,10 +7766,10 @@
         <v>7</v>
       </c>
       <c r="V74" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="W74" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
     </row>
     <row r="75">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_30.jpg</t>
+          <t>stimuli/lamp/lamp_08.jpg</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_23.jpg</t>
+          <t>stimuli/chair/chair_16.jpg</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -7821,38 +7821,38 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>lamp</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P75" t="n">
-        <v>0.33</v>
+        <v>0.53</v>
       </c>
       <c r="Q75" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S75" t="n">
@@ -7865,10 +7865,10 @@
         <v>10</v>
       </c>
       <c r="V75" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="W75" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="76">
@@ -7900,12 +7900,12 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_08.jpg</t>
+          <t>stimuli/bread/bread_49.jpg</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_22.jpg</t>
+          <t>stimuli/glasses/glasses_02.jpg</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -7920,38 +7920,38 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>lamp</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>glasses</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P76" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="Q76" t="n">
-        <v>0.2</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S76" t="n">
@@ -7964,10 +7964,10 @@
         <v>8</v>
       </c>
       <c r="V76" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="W76" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
     </row>
     <row r="77">
@@ -7999,12 +7999,12 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>stimuli/glasses/glasses_02.jpg</t>
+          <t>stimuli/phone/phone_04.jpg</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_23.jpg</t>
+          <t>stimuli/flower/flower_22.jpg</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -8019,12 +8019,12 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>glasses</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
@@ -8034,19 +8034,19 @@
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P77" t="n">
-        <v>0.75</v>
+        <v>0.73</v>
       </c>
       <c r="Q77" t="n">
-        <v>0.33</v>
+        <v>0.27</v>
       </c>
       <c r="R77" t="inlineStr">
         <is>
@@ -8063,10 +8063,10 @@
         <v>3</v>
       </c>
       <c r="V77" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="W77" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="78">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_35.jpg</t>
+          <t>stimuli/lamp/lamp_08.jpg</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_16.jpg</t>
+          <t>stimuli/ball/ball_23.jpg</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -8118,12 +8118,12 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>lamp</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
@@ -8133,19 +8133,19 @@
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P78" t="n">
-        <v>0.67</v>
+        <v>0.73</v>
       </c>
       <c r="Q78" t="n">
-        <v>0.47</v>
+        <v>0.4</v>
       </c>
       <c r="R78" t="inlineStr">
         <is>
@@ -8162,10 +8162,10 @@
         <v>15</v>
       </c>
       <c r="V78" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="W78" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="79">
@@ -8197,12 +8197,12 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_08.jpg</t>
+          <t>stimuli/dog/dog_30.jpg</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_26.jpg</t>
+          <t>stimuli/phone/phone_04.jpg</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -8217,38 +8217,38 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>lamp</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P79" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="Q79" t="n">
-        <v>0.33</v>
+        <v>0.26</v>
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S79" t="n">
@@ -8261,10 +8261,10 @@
         <v>18</v>
       </c>
       <c r="V79" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="W79" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
     </row>
     <row r="80">
@@ -8296,12 +8296,12 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_04.jpg</t>
+          <t>stimuli/bicycle/bicycle_28.jpg</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>stimuli/house/house_10.jpg</t>
+          <t>stimuli/pencil/pencil_15.jpg</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -8316,38 +8316,38 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>pencil</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P80" t="n">
-        <v>0.58</v>
+        <v>0.53</v>
       </c>
       <c r="Q80" t="n">
-        <v>0.36</v>
+        <v>0.2</v>
       </c>
       <c r="R80" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S80" t="n">
@@ -8360,10 +8360,10 @@
         <v>11</v>
       </c>
       <c r="V80" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="W80" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
     </row>
     <row r="81">
@@ -8395,7 +8395,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_04.jpg</t>
+          <t>stimuli/hand/hand_20.jpg</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -8415,7 +8415,7 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -8439,7 +8439,7 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>0.47</v>
+        <v>0.53</v>
       </c>
       <c r="Q81" t="n">
         <v>0.31</v>
@@ -8459,7 +8459,7 @@
         <v>5</v>
       </c>
       <c r="V81" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="W81" t="n">
         <v>17</v>
@@ -8494,7 +8494,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_20.jpg</t>
+          <t>stimuli/house/house_10.jpg</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -8514,7 +8514,7 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>house</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -8524,28 +8524,28 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P82" t="n">
-        <v>0.58</v>
+        <v>0.47</v>
       </c>
       <c r="Q82" t="n">
         <v>0.31</v>
       </c>
       <c r="R82" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S82" t="n">
@@ -8558,7 +8558,7 @@
         <v>3</v>
       </c>
       <c r="V82" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W82" t="n">
         <v>16</v>
@@ -8593,12 +8593,12 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_28.jpg</t>
+          <t>stimuli/chair/chair_04.jpg</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_04.jpg</t>
+          <t>stimuli/hammer/hammer_09.jpg</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -8613,38 +8613,38 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P83" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.75</v>
       </c>
       <c r="Q83" t="n">
-        <v>0.58</v>
+        <v>0.47</v>
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S83" t="n">
@@ -8657,10 +8657,10 @@
         <v>10</v>
       </c>
       <c r="V83" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="W83" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="84">
@@ -8727,12 +8727,12 @@
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P84" t="n">
@@ -8791,12 +8791,12 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_09.jpg</t>
+          <t>stimuli/ball/ball_04.jpg</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>stimuli/pencil/pencil_15.jpg</t>
+          <t>stimuli/phone/phone_22.jpg</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -8811,12 +8811,12 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>pencil</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
@@ -8835,10 +8835,10 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>0.58</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="Q85" t="n">
-        <v>0.47</v>
+        <v>0.53</v>
       </c>
       <c r="R85" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         <v>4</v>
       </c>
       <c r="V85" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="W85" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="86">
@@ -8890,14 +8890,14 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
+          <t>stimuli/hammer/hammer_09.jpg</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
           <t>stimuli/car/car_04.jpg</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>stimuli/jacket/jacket_06.jpg</t>
-        </is>
-      </c>
       <c r="I86" t="inlineStr">
         <is>
           <t>chair</t>
@@ -8910,38 +8910,38 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
+          <t>hammer</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
           <t>car</t>
         </is>
       </c>
-      <c r="L86" t="inlineStr">
-        <is>
-          <t>jacket</t>
-        </is>
-      </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P86" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="Q86" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q86" t="n">
-        <v>0.2</v>
-      </c>
       <c r="R86" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S86" t="n">
@@ -8954,10 +8954,10 @@
         <v>2</v>
       </c>
       <c r="V86" t="n">
+        <v>7</v>
+      </c>
+      <c r="W86" t="n">
         <v>11</v>
-      </c>
-      <c r="W86" t="n">
-        <v>10</v>
       </c>
     </row>
     <row r="87">
@@ -8989,12 +8989,12 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_25.jpg</t>
+          <t>stimuli/house/house_10.jpg</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_21.jpg</t>
+          <t>stimuli/jacket/jacket_06.jpg</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -9009,12 +9009,12 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>house</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
@@ -9033,10 +9033,10 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>0.33</v>
+        <v>0.75</v>
       </c>
       <c r="Q87" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="R87" t="inlineStr">
         <is>
@@ -9053,10 +9053,10 @@
         <v>8</v>
       </c>
       <c r="V87" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="W87" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="88">
@@ -9088,12 +9088,12 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>stimuli/house/house_10.jpg</t>
+          <t>stimuli/dog/dog_11.jpg</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>stimuli/phone/phone_22.jpg</t>
+          <t>stimuli/flower/flower_21.jpg</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -9108,12 +9108,12 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
@@ -9123,19 +9123,19 @@
       </c>
       <c r="N88" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P88" t="n">
-        <v>0.8</v>
+        <v>0.47</v>
       </c>
       <c r="Q88" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.27</v>
       </c>
       <c r="R88" t="inlineStr">
         <is>
@@ -9152,10 +9152,10 @@
         <v>1</v>
       </c>
       <c r="V88" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="W88" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
     </row>
     <row r="89">
@@ -9187,12 +9187,12 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_09.jpg</t>
+          <t>stimuli/car/car_04.jpg</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>stimuli/pencil/pencil_15.jpg</t>
+          <t>stimuli/bread/bread_25.jpg</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -9207,17 +9207,17 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>car</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>pencil</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N89" t="inlineStr">
@@ -9227,18 +9227,18 @@
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P89" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="Q89" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.47</v>
       </c>
       <c r="R89" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S89" t="n">
@@ -9251,10 +9251,10 @@
         <v>9</v>
       </c>
       <c r="V89" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="W89" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
     </row>
     <row r="90">
@@ -9286,12 +9286,12 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>stimuli/car/car_04.jpg</t>
+          <t>stimuli/lamp/lamp_30.jpg</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_21.jpg</t>
+          <t>stimuli/jacket/jacket_06.jpg</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -9306,12 +9306,12 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>car</t>
+          <t>lamp</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
@@ -9321,19 +9321,19 @@
       </c>
       <c r="N90" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O90" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P90" t="n">
-        <v>0.67</v>
+        <v>0.73</v>
       </c>
       <c r="Q90" t="n">
-        <v>0.4</v>
+        <v>0.47</v>
       </c>
       <c r="R90" t="inlineStr">
         <is>
@@ -9350,10 +9350,10 @@
         <v>7</v>
       </c>
       <c r="V90" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="W90" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="91">
@@ -9385,12 +9385,12 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_11.jpg</t>
+          <t>stimuli/bread/bread_25.jpg</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_06.jpg</t>
+          <t>stimuli/chair/chair_04.jpg</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -9405,38 +9405,38 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N91" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O91" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P91" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="Q91" t="n">
-        <v>0.53</v>
+        <v>0.4</v>
       </c>
       <c r="R91" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S91" t="n">
@@ -9449,10 +9449,10 @@
         <v>17</v>
       </c>
       <c r="V91" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="W91" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="92">
@@ -9588,7 +9588,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_30.jpg</t>
+          <t>stimuli/glasses/glasses_02.jpg</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -9608,17 +9608,17 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>glasses</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N93" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O93" t="inlineStr">
@@ -9630,11 +9630,11 @@
         <v>0.64</v>
       </c>
       <c r="Q93" t="n">
-        <v>0.36</v>
+        <v>0.2</v>
       </c>
       <c r="R93" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S93" t="n">
@@ -9650,7 +9650,7 @@
         <v>4</v>
       </c>
       <c r="W93" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
     </row>
     <row r="94">
@@ -9682,7 +9682,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_30.jpg</t>
+          <t>stimuli/house/house_05.jpg</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -9702,7 +9702,7 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>house</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
@@ -9726,7 +9726,7 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="Q94" t="n">
         <v>0.36</v>
@@ -9746,7 +9746,7 @@
         <v>2</v>
       </c>
       <c r="V94" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="W94" t="n">
         <v>3</v>
@@ -9781,7 +9781,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_35.jpg</t>
+          <t>stimuli/hammer/hammer_26.jpg</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -9801,7 +9801,7 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
@@ -9811,12 +9811,12 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N95" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O95" t="inlineStr">
@@ -9825,14 +9825,14 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>0.53</v>
+        <v>0.58</v>
       </c>
       <c r="Q95" t="n">
         <v>0.31</v>
       </c>
       <c r="R95" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S95" t="n">
@@ -9845,7 +9845,7 @@
         <v>9</v>
       </c>
       <c r="V95" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="W95" t="n">
         <v>18</v>
@@ -9880,12 +9880,12 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_26.jpg</t>
+          <t>stimuli/flower/flower_22.jpg</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_30.jpg</t>
+          <t>stimuli/key/key_10.jpg</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -9900,12 +9900,12 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>key</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
@@ -9915,19 +9915,19 @@
       </c>
       <c r="N96" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O96" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P96" t="n">
-        <v>0.64</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="Q96" t="n">
-        <v>0.53</v>
+        <v>0.42</v>
       </c>
       <c r="R96" t="inlineStr">
         <is>
@@ -9944,10 +9944,10 @@
         <v>5</v>
       </c>
       <c r="V96" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W96" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
     </row>
     <row r="97">
@@ -9979,12 +9979,12 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_22.jpg</t>
+          <t>stimuli/hand/hand_30.jpg</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_49.jpg</t>
+          <t>stimuli/glasses/glasses_02.jpg</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -9999,12 +9999,12 @@
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>glasses</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
@@ -10014,19 +10014,19 @@
       </c>
       <c r="N97" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O97" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P97" t="n">
-        <v>0.75</v>
+        <v>0.58</v>
       </c>
       <c r="Q97" t="n">
-        <v>0.53</v>
+        <v>0.42</v>
       </c>
       <c r="R97" t="inlineStr">
         <is>
@@ -10043,10 +10043,10 @@
         <v>4</v>
       </c>
       <c r="V97" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="W97" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
     </row>
     <row r="98">
@@ -10078,12 +10078,12 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>stimuli/phone/phone_04.jpg</t>
+          <t>stimuli/jacket/jacket_35.jpg</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_35.jpg</t>
+          <t>stimuli/key/key_10.jpg</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -10098,17 +10098,17 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>key</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N98" t="inlineStr">
@@ -10118,18 +10118,18 @@
       </c>
       <c r="O98" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P98" t="n">
-        <v>0.4</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="Q98" t="n">
-        <v>0.27</v>
+        <v>0.53</v>
       </c>
       <c r="R98" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S98" t="n">
@@ -10142,10 +10142,10 @@
         <v>1</v>
       </c>
       <c r="V98" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="W98" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
     </row>
     <row r="99">
@@ -10177,12 +10177,12 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_35.jpg</t>
+          <t>stimuli/bicycle/bicycle_35.jpg</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>stimuli/key/key_10.jpg</t>
+          <t>stimuli/dog/dog_30.jpg</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -10197,12 +10197,12 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
@@ -10212,19 +10212,19 @@
       </c>
       <c r="N99" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O99" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P99" t="n">
-        <v>0.75</v>
+        <v>0.33</v>
       </c>
       <c r="Q99" t="n">
-        <v>0.58</v>
+        <v>0.2</v>
       </c>
       <c r="R99" t="inlineStr">
         <is>
@@ -10241,10 +10241,10 @@
         <v>6</v>
       </c>
       <c r="V99" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="W99" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="100">
@@ -10276,12 +10276,12 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_49.jpg</t>
+          <t>stimuli/phone/phone_04.jpg</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>stimuli/house/house_05.jpg</t>
+          <t>stimuli/chair/chair_16.jpg</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -10296,12 +10296,12 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
@@ -10320,10 +10320,10 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.53</v>
       </c>
       <c r="Q100" t="n">
-        <v>0.33</v>
+        <v>0.2</v>
       </c>
       <c r="R100" t="inlineStr">
         <is>
@@ -10340,10 +10340,10 @@
         <v>7</v>
       </c>
       <c r="V100" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="W100" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="101">
@@ -10380,7 +10380,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_16.jpg</t>
+          <t>stimuli/ball/ball_23.jpg</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -10400,17 +10400,17 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N101" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O101" t="inlineStr">
@@ -10422,11 +10422,11 @@
         <v>0.53</v>
       </c>
       <c r="Q101" t="n">
-        <v>0.27</v>
+        <v>0.2</v>
       </c>
       <c r="R101" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S101" t="n">
@@ -10442,7 +10442,7 @@
         <v>14</v>
       </c>
       <c r="W101" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="102">
@@ -10474,12 +10474,12 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>stimuli/phone/phone_04.jpg</t>
+          <t>stimuli/house/house_05.jpg</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_23.jpg</t>
+          <t>stimuli/chair/chair_16.jpg</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -10494,38 +10494,38 @@
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>house</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N102" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O102" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P102" t="n">
-        <v>0.67</v>
+        <v>0.47</v>
       </c>
       <c r="Q102" t="n">
-        <v>0.27</v>
+        <v>0.33</v>
       </c>
       <c r="R102" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S102" t="n">
@@ -10538,10 +10538,10 @@
         <v>8</v>
       </c>
       <c r="V102" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="W102" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="103">
@@ -10573,12 +10573,12 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_08.jpg</t>
+          <t>stimuli/phone/phone_04.jpg</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_26.jpg</t>
+          <t>stimuli/house/house_05.jpg</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -10593,38 +10593,38 @@
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>lamp</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>house</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N103" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O103" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P103" t="n">
-        <v>0.67</v>
+        <v>0.73</v>
       </c>
       <c r="Q103" t="n">
-        <v>0.2</v>
+        <v>0.53</v>
       </c>
       <c r="R103" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S103" t="n">
@@ -10637,10 +10637,10 @@
         <v>3</v>
       </c>
       <c r="V103" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="W103" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="104">
@@ -10672,14 +10672,14 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
+          <t>stimuli/bicycle/bicycle_35.jpg</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
           <t>stimuli/dog/dog_30.jpg</t>
         </is>
       </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>stimuli/ball/ball_23.jpg</t>
-        </is>
-      </c>
       <c r="I104" t="inlineStr">
         <is>
           <t>bread</t>
@@ -10692,38 +10692,38 @@
       </c>
       <c r="K104" t="inlineStr">
         <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
           <t>dog</t>
         </is>
       </c>
-      <c r="L104" t="inlineStr">
-        <is>
-          <t>ball</t>
-        </is>
-      </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N104" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O104" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P104" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="Q104" t="n">
         <v>0.53</v>
       </c>
-      <c r="Q104" t="n">
-        <v>0.4</v>
-      </c>
       <c r="R104" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S104" t="n">
@@ -10736,10 +10736,10 @@
         <v>15</v>
       </c>
       <c r="V104" t="n">
+        <v>2</v>
+      </c>
+      <c r="W104" t="n">
         <v>5</v>
-      </c>
-      <c r="W104" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="105">
@@ -10776,7 +10776,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_16.jpg</t>
+          <t>stimuli/flower/flower_22.jpg</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -10796,7 +10796,7 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
@@ -10818,7 +10818,7 @@
         <v>0.8</v>
       </c>
       <c r="Q105" t="n">
-        <v>0.53</v>
+        <v>0.4</v>
       </c>
       <c r="R105" t="inlineStr">
         <is>
@@ -10838,7 +10838,7 @@
         <v>14</v>
       </c>
       <c r="W105" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/psychopy_exp_files/sequences/learning_block2_fixed-middle-10_27.xlsx
+++ b/psychopy_exp_files/sequences/learning_block2_fixed-middle-10_27.xlsx
@@ -574,12 +574,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_04.jpg</t>
+          <t>stimuli/ball/ball_04.jpg</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>stimuli/house/house_10.jpg</t>
+          <t>stimuli/dog/dog_11.jpg</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -594,12 +594,12 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -638,10 +638,10 @@
         <v>11</v>
       </c>
       <c r="V2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="W2" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3">
@@ -668,12 +668,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_11.jpg</t>
+          <t>stimuli/hand/hand_20.jpg</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_06.jpg</t>
+          <t>stimuli/chair/chair_04.jpg</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -688,12 +688,12 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -734,10 +734,10 @@
         <v>11</v>
       </c>
       <c r="U3" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="V3" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="W3" t="n">
         <v>16</v>
@@ -762,12 +762,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_11.jpg</t>
+          <t>stimuli/hand/hand_20.jpg</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_25.jpg</t>
+          <t>stimuli/house/house_10.jpg</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>house</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -830,10 +830,10 @@
         <v>4</v>
       </c>
       <c r="T4" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="U4" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="V4" t="n">
         <v>17</v>
@@ -861,42 +861,42 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
+          <t>stimuli/house/house_10.jpg</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>stimuli/chair/chair_04.jpg</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>stimuli/flower/flower_21.jpg</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
           <t>stimuli/bread/bread_25.jpg</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>stimuli/jacket/jacket_06.jpg</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>stimuli/bicycle/bicycle_28.jpg</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>stimuli/hammer/hammer_09.jpg</t>
-        </is>
-      </c>
       <c r="I5" t="inlineStr">
         <is>
+          <t>house</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>chair</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>flower</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
           <t>bread</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>jacket</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>bicycle</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>hammer</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -929,16 +929,16 @@
         <v>5</v>
       </c>
       <c r="T5" t="n">
+        <v>9</v>
+      </c>
+      <c r="U5" t="n">
+        <v>4</v>
+      </c>
+      <c r="V5" t="n">
+        <v>6</v>
+      </c>
+      <c r="W5" t="n">
         <v>3</v>
-      </c>
-      <c r="U5" t="n">
-        <v>10</v>
-      </c>
-      <c r="V5" t="n">
-        <v>2</v>
-      </c>
-      <c r="W5" t="n">
-        <v>7</v>
       </c>
     </row>
     <row r="6">
@@ -960,42 +960,42 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
+          <t>stimuli/chair/chair_04.jpg</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
           <t>stimuli/jacket/jacket_06.jpg</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>stimuli/flower/flower_21.jpg</t>
-        </is>
-      </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_04.jpg</t>
+          <t>stimuli/ball/ball_04.jpg</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_04.jpg</t>
+          <t>stimuli/bicycle/bicycle_28.jpg</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
+          <t>chair</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>jacket</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>flower</t>
-        </is>
-      </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -1028,16 +1028,16 @@
         <v>6</v>
       </c>
       <c r="T6" t="n">
+        <v>4</v>
+      </c>
+      <c r="U6" t="n">
         <v>10</v>
       </c>
-      <c r="U6" t="n">
-        <v>6</v>
-      </c>
       <c r="V6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="W6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -1059,17 +1059,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_21.jpg</t>
+          <t>stimuli/jacket/jacket_06.jpg</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_04.jpg</t>
+          <t>stimuli/ball/ball_04.jpg</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_20.jpg</t>
+          <t>stimuli/hammer/hammer_09.jpg</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1079,17 +1079,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1127,13 +1127,13 @@
         <v>7</v>
       </c>
       <c r="T7" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="U7" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="V7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W7" t="n">
         <v>16</v>
@@ -1158,42 +1158,42 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
+          <t>stimuli/ball/ball_04.jpg</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>stimuli/flower/flower_21.jpg</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>stimuli/hand/hand_20.jpg</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
           <t>stimuli/chair/chair_04.jpg</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>stimuli/bicycle/bicycle_28.jpg</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>stimuli/dog/dog_11.jpg</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>stimuli/jacket/jacket_06.jpg</t>
-        </is>
-      </c>
       <c r="I8" t="inlineStr">
         <is>
+          <t>ball</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>flower</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>hand</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
           <t>chair</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>bicycle</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>dog</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>jacket</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1226,16 +1226,16 @@
         <v>8</v>
       </c>
       <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="n">
+        <v>6</v>
+      </c>
+      <c r="V8" t="n">
+        <v>8</v>
+      </c>
+      <c r="W8" t="n">
         <v>4</v>
-      </c>
-      <c r="U8" t="n">
-        <v>2</v>
-      </c>
-      <c r="V8" t="n">
-        <v>5</v>
-      </c>
-      <c r="W8" t="n">
-        <v>10</v>
       </c>
     </row>
     <row r="9">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_28.jpg</t>
+          <t>stimuli/flower/flower_21.jpg</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_20.jpg</t>
+          <t>stimuli/hammer/hammer_09.jpg</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1272,17 +1272,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_25.jpg</t>
+          <t>stimuli/house/house_10.jpg</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1292,7 +1292,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>house</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1325,16 +1325,16 @@
         <v>9</v>
       </c>
       <c r="T9" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="U9" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V9" t="n">
         <v>14</v>
       </c>
       <c r="W9" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10">
@@ -1356,12 +1356,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_20.jpg</t>
+          <t>stimuli/hammer/hammer_09.jpg</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_04.jpg</t>
+          <t>stimuli/bicycle/bicycle_28.jpg</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1371,17 +1371,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_21.jpg</t>
+          <t>stimuli/jacket/jacket_06.jpg</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1391,7 +1391,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1424,16 +1424,16 @@
         <v>10</v>
       </c>
       <c r="T10" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V10" t="n">
         <v>11</v>
       </c>
       <c r="W10" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11">
@@ -1455,17 +1455,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_04.jpg</t>
+          <t>stimuli/bicycle/bicycle_28.jpg</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>stimuli/house/house_10.jpg</t>
+          <t>stimuli/dog/dog_11.jpg</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_09.jpg</t>
+          <t>stimuli/bread/bread_25.jpg</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1475,17 +1475,17 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1523,13 +1523,13 @@
         <v>11</v>
       </c>
       <c r="T11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U11" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="V11" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="W11" t="n">
         <v>16</v>
@@ -1554,12 +1554,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>stimuli/house/house_10.jpg</t>
+          <t>stimuli/dog/dog_11.jpg</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_09.jpg</t>
+          <t>stimuli/bread/bread_25.jpg</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1569,17 +1569,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_06.jpg</t>
+          <t>stimuli/chair/chair_04.jpg</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1622,16 +1622,16 @@
         <v>12</v>
       </c>
       <c r="T12" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="U12" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="V12" t="n">
         <v>14</v>
       </c>
       <c r="W12" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_09.jpg</t>
+          <t>stimuli/bread/bread_25.jpg</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_25.jpg</t>
+          <t>stimuli/house/house_10.jpg</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1688,7 +1688,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>house</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1721,7 +1721,7 @@
         <v>13</v>
       </c>
       <c r="T13" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="U13" t="n">
         <v>17</v>
@@ -1730,7 +1730,7 @@
         <v>11</v>
       </c>
       <c r="W13" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14">
@@ -1762,7 +1762,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_21.jpg</t>
+          <t>stimuli/jacket/jacket_06.jpg</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1826,7 +1826,7 @@
         <v>16</v>
       </c>
       <c r="V14" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="W14" t="n">
         <v>14</v>
@@ -1861,12 +1861,12 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_16.jpg</t>
+          <t>stimuli/ball/ball_23.jpg</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_49.jpg</t>
+          <t>stimuli/house/house_05.jpg</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>house</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1925,10 +1925,10 @@
         <v>14</v>
       </c>
       <c r="V15" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="W15" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_35.jpg</t>
+          <t>stimuli/flower/flower_22.jpg</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_30.jpg</t>
+          <t>stimuli/hammer/hammer_26.jpg</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1975,12 +1975,12 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -2021,10 +2021,10 @@
         <v>14</v>
       </c>
       <c r="U16" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="V16" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W16" t="n">
         <v>18</v>
@@ -2049,17 +2049,17 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_35.jpg</t>
+          <t>stimuli/flower/flower_22.jpg</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>stimuli/house/house_05.jpg</t>
+          <t>stimuli/dog/dog_30.jpg</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_16.jpg</t>
+          <t>stimuli/ball/ball_23.jpg</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2069,17 +2069,17 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -2117,13 +2117,13 @@
         <v>4</v>
       </c>
       <c r="T17" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="U17" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="V17" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="W17" t="n">
         <v>15</v>
@@ -2148,17 +2148,17 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>stimuli/house/house_05.jpg</t>
+          <t>stimuli/dog/dog_30.jpg</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_30.jpg</t>
+          <t>stimuli/hand/hand_30.jpg</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_35.jpg</t>
+          <t>stimuli/chair/chair_16.jpg</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2168,17 +2168,17 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -2216,13 +2216,13 @@
         <v>5</v>
       </c>
       <c r="T18" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="U18" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="V18" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="W18" t="n">
         <v>18</v>
@@ -2247,12 +2247,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_30.jpg</t>
+          <t>stimuli/hand/hand_30.jpg</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_16.jpg</t>
+          <t>stimuli/ball/ball_23.jpg</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2262,17 +2262,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_35.jpg</t>
+          <t>stimuli/flower/flower_22.jpg</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -2315,16 +2315,16 @@
         <v>6</v>
       </c>
       <c r="T19" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="U19" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="V19" t="n">
         <v>17</v>
       </c>
       <c r="W19" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20">
@@ -2346,17 +2346,17 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_16.jpg</t>
+          <t>stimuli/ball/ball_23.jpg</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_23.jpg</t>
+          <t>stimuli/bicycle/bicycle_35.jpg</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_22.jpg</t>
+          <t>stimuli/jacket/jacket_35.jpg</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2366,17 +2366,17 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -2414,13 +2414,13 @@
         <v>7</v>
       </c>
       <c r="T20" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V20" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="W20" t="n">
         <v>15</v>
@@ -2445,17 +2445,17 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_23.jpg</t>
+          <t>stimuli/bicycle/bicycle_35.jpg</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_22.jpg</t>
+          <t>stimuli/jacket/jacket_35.jpg</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_26.jpg</t>
+          <t>stimuli/bread/bread_49.jpg</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2465,17 +2465,17 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -2513,13 +2513,13 @@
         <v>8</v>
       </c>
       <c r="T21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U21" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="V21" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="W21" t="n">
         <v>18</v>
@@ -2544,42 +2544,42 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
+          <t>stimuli/jacket/jacket_35.jpg</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>stimuli/bread/bread_49.jpg</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
           <t>stimuli/flower/flower_22.jpg</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>stimuli/hammer/hammer_26.jpg</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>stimuli/bicycle/bicycle_35.jpg</t>
-        </is>
-      </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_30.jpg</t>
+          <t>stimuli/hand/hand_30.jpg</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
+          <t>jacket</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>bread</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
           <t>flower</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>hammer</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>bicycle</t>
-        </is>
-      </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -2612,16 +2612,16 @@
         <v>9</v>
       </c>
       <c r="T22" t="n">
+        <v>10</v>
+      </c>
+      <c r="U22" t="n">
+        <v>3</v>
+      </c>
+      <c r="V22" t="n">
         <v>6</v>
       </c>
-      <c r="U22" t="n">
-        <v>7</v>
-      </c>
-      <c r="V22" t="n">
-        <v>2</v>
-      </c>
       <c r="W22" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="23">
@@ -2643,12 +2643,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_26.jpg</t>
+          <t>stimuli/bread/bread_49.jpg</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_35.jpg</t>
+          <t>stimuli/chair/chair_16.jpg</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -2658,17 +2658,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>stimuli/house/house_05.jpg</t>
+          <t>stimuli/dog/dog_30.jpg</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -2678,7 +2678,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -2711,16 +2711,16 @@
         <v>10</v>
       </c>
       <c r="T23" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="U23" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="V23" t="n">
         <v>18</v>
       </c>
       <c r="W23" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24">
@@ -2742,42 +2742,42 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
+          <t>stimuli/chair/chair_16.jpg</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>stimuli/hammer/hammer_26.jpg</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>stimuli/lamp/lamp_08.jpg</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
           <t>stimuli/jacket/jacket_35.jpg</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>stimuli/hand/hand_30.jpg</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>stimuli/lamp/lamp_08.jpg</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>stimuli/flower/flower_22.jpg</t>
-        </is>
-      </c>
       <c r="I24" t="inlineStr">
         <is>
+          <t>chair</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>hammer</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>lamp</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
           <t>jacket</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>hand</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>lamp</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>flower</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -2810,16 +2810,16 @@
         <v>11</v>
       </c>
       <c r="T24" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="U24" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V24" t="n">
         <v>14</v>
       </c>
       <c r="W24" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="25">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_30.jpg</t>
+          <t>stimuli/hammer/hammer_26.jpg</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_49.jpg</t>
+          <t>stimuli/house/house_05.jpg</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -2856,17 +2856,17 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_23.jpg</t>
+          <t>stimuli/bicycle/bicycle_35.jpg</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>house</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2909,16 +2909,16 @@
         <v>12</v>
       </c>
       <c r="T25" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U25" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="V25" t="n">
         <v>17</v>
       </c>
       <c r="W25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26">
@@ -2940,7 +2940,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_49.jpg</t>
+          <t>stimuli/house/house_05.jpg</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -2950,17 +2950,17 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_35.jpg</t>
+          <t>stimuli/flower/flower_22.jpg</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_30.jpg</t>
+          <t>stimuli/hand/hand_30.jpg</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>house</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2970,12 +2970,12 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -3008,16 +3008,16 @@
         <v>13</v>
       </c>
       <c r="T26" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="U26" t="n">
         <v>15</v>
       </c>
       <c r="V26" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="W26" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="27">
@@ -3054,7 +3054,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_23.jpg</t>
+          <t>stimuli/bicycle/bicycle_35.jpg</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3074,7 +3074,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -3116,7 +3116,7 @@
         <v>14</v>
       </c>
       <c r="W27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28">
@@ -3148,7 +3148,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_25.jpg</t>
+          <t>stimuli/house/house_10.jpg</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3168,7 +3168,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>house</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -3212,7 +3212,7 @@
         <v>11</v>
       </c>
       <c r="V28" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="W28" t="n">
         <v>16</v>
@@ -3242,14 +3242,14 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
+          <t>stimuli/hand/hand_20.jpg</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
           <t>stimuli/dog/dog_11.jpg</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>stimuli/house/house_10.jpg</t>
-        </is>
-      </c>
       <c r="H29" t="inlineStr">
         <is>
           <t>stimuli/phone/phone_22.jpg</t>
@@ -3262,12 +3262,12 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
+          <t>hand</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
           <t>dog</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>house</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -3308,10 +3308,10 @@
         <v>11</v>
       </c>
       <c r="U29" t="n">
+        <v>8</v>
+      </c>
+      <c r="V29" t="n">
         <v>5</v>
-      </c>
-      <c r="V29" t="n">
-        <v>9</v>
       </c>
       <c r="W29" t="n">
         <v>17</v>
@@ -3336,17 +3336,17 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_11.jpg</t>
+          <t>stimuli/hand/hand_20.jpg</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_25.jpg</t>
+          <t>stimuli/house/house_10.jpg</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_04.jpg</t>
+          <t>stimuli/ball/ball_04.jpg</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -3356,17 +3356,17 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>house</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -3404,13 +3404,13 @@
         <v>4</v>
       </c>
       <c r="T30" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="U30" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="V30" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="W30" t="n">
         <v>16</v>
@@ -3435,17 +3435,17 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_25.jpg</t>
+          <t>stimuli/house/house_10.jpg</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_06.jpg</t>
+          <t>stimuli/chair/chair_04.jpg</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_28.jpg</t>
+          <t>stimuli/flower/flower_21.jpg</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -3455,17 +3455,17 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>house</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -3503,13 +3503,13 @@
         <v>5</v>
       </c>
       <c r="T31" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="U31" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="V31" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="W31" t="n">
         <v>14</v>
@@ -3534,17 +3534,17 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
+          <t>stimuli/chair/chair_04.jpg</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
           <t>stimuli/jacket/jacket_06.jpg</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>stimuli/flower/flower_21.jpg</t>
-        </is>
-      </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_09.jpg</t>
+          <t>stimuli/bread/bread_25.jpg</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -3554,17 +3554,17 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
+          <t>chair</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
           <t>jacket</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>flower</t>
-        </is>
-      </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -3602,13 +3602,13 @@
         <v>6</v>
       </c>
       <c r="T32" t="n">
+        <v>4</v>
+      </c>
+      <c r="U32" t="n">
         <v>10</v>
       </c>
-      <c r="U32" t="n">
-        <v>6</v>
-      </c>
       <c r="V32" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="W32" t="n">
         <v>16</v>
@@ -3633,12 +3633,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_21.jpg</t>
+          <t>stimuli/jacket/jacket_06.jpg</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_04.jpg</t>
+          <t>stimuli/ball/ball_04.jpg</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -3648,17 +3648,17 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_11.jpg</t>
+          <t>stimuli/hand/hand_20.jpg</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -3668,7 +3668,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -3701,16 +3701,16 @@
         <v>7</v>
       </c>
       <c r="T33" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="U33" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="V33" t="n">
         <v>14</v>
       </c>
       <c r="W33" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="34">
@@ -3732,19 +3732,19 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_04.jpg</t>
+          <t>stimuli/ball/ball_04.jpg</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
+          <t>stimuli/flower/flower_21.jpg</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
           <t>stimuli/bicycle/bicycle_28.jpg</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>stimuli/ball/ball_04.jpg</t>
-        </is>
-      </c>
       <c r="H34" t="inlineStr">
         <is>
           <t>stimuli/phone/phone_22.jpg</t>
@@ -3752,17 +3752,17 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
+          <t>flower</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
           <t>bicycle</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>ball</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -3800,13 +3800,13 @@
         <v>8</v>
       </c>
       <c r="T34" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U34" t="n">
+        <v>6</v>
+      </c>
+      <c r="V34" t="n">
         <v>2</v>
-      </c>
-      <c r="V34" t="n">
-        <v>1</v>
       </c>
       <c r="W34" t="n">
         <v>17</v>
@@ -3831,42 +3831,42 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_28.jpg</t>
+          <t>stimuli/flower/flower_21.jpg</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
+          <t>stimuli/hammer/hammer_09.jpg</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
           <t>stimuli/hand/hand_20.jpg</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>stimuli/dog/dog_11.jpg</t>
-        </is>
-      </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_21.jpg</t>
+          <t>stimuli/jacket/jacket_06.jpg</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
+          <t>hammer</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
           <t>hand</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>dog</t>
-        </is>
-      </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -3899,16 +3899,16 @@
         <v>9</v>
       </c>
       <c r="T35" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="U35" t="n">
+        <v>7</v>
+      </c>
+      <c r="V35" t="n">
         <v>8</v>
       </c>
-      <c r="V35" t="n">
-        <v>5</v>
-      </c>
       <c r="W35" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="36">
@@ -3930,12 +3930,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_20.jpg</t>
+          <t>stimuli/hammer/hammer_09.jpg</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_04.jpg</t>
+          <t>stimuli/bicycle/bicycle_28.jpg</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -3950,12 +3950,12 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -3998,10 +3998,10 @@
         <v>10</v>
       </c>
       <c r="T36" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V36" t="n">
         <v>16</v>
@@ -4029,12 +4029,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_04.jpg</t>
+          <t>stimuli/bicycle/bicycle_28.jpg</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>stimuli/house/house_10.jpg</t>
+          <t>stimuli/dog/dog_11.jpg</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -4044,17 +4044,17 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_06.jpg</t>
+          <t>stimuli/chair/chair_04.jpg</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -4064,7 +4064,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -4097,16 +4097,16 @@
         <v>11</v>
       </c>
       <c r="T37" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U37" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="V37" t="n">
         <v>14</v>
       </c>
       <c r="W37" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="38">
@@ -4128,42 +4128,42 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>stimuli/house/house_10.jpg</t>
+          <t>stimuli/dog/dog_11.jpg</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
+          <t>stimuli/bread/bread_25.jpg</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>stimuli/pencil/pencil_15.jpg</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
           <t>stimuli/hammer/hammer_09.jpg</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>stimuli/pencil/pencil_15.jpg</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>stimuli/hand/hand_20.jpg</t>
-        </is>
-      </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
+          <t>bread</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>pencil</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
           <t>hammer</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>pencil</t>
-        </is>
-      </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>hand</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -4196,16 +4196,16 @@
         <v>12</v>
       </c>
       <c r="T38" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="U38" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="V38" t="n">
         <v>16</v>
       </c>
       <c r="W38" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="39">
@@ -4227,7 +4227,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_09.jpg</t>
+          <t>stimuli/bread/bread_25.jpg</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -4242,12 +4242,12 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_06.jpg</t>
+          <t>stimuli/chair/chair_04.jpg</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -4262,7 +4262,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -4295,7 +4295,7 @@
         <v>13</v>
       </c>
       <c r="T39" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="U39" t="n">
         <v>17</v>
@@ -4304,7 +4304,7 @@
         <v>14</v>
       </c>
       <c r="W39" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="40">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_25.jpg</t>
+          <t>stimuli/house/house_10.jpg</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -4361,7 +4361,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>house</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -4403,7 +4403,7 @@
         <v>11</v>
       </c>
       <c r="W40" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="41">
@@ -4435,7 +4435,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_35.jpg</t>
+          <t>stimuli/flower/flower_22.jpg</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -4455,7 +4455,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -4499,7 +4499,7 @@
         <v>14</v>
       </c>
       <c r="V41" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="W41" t="n">
         <v>15</v>
@@ -4529,12 +4529,12 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_35.jpg</t>
+          <t>stimuli/flower/flower_22.jpg</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_49.jpg</t>
+          <t>stimuli/house/house_05.jpg</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -4549,12 +4549,12 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>house</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -4595,10 +4595,10 @@
         <v>14</v>
       </c>
       <c r="U42" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="V42" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="W42" t="n">
         <v>18</v>
@@ -4623,42 +4623,42 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_35.jpg</t>
+          <t>stimuli/flower/flower_22.jpg</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
+          <t>stimuli/dog/dog_30.jpg</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>stimuli/bread/bread_49.jpg</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
           <t>stimuli/house/house_05.jpg</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>stimuli/hammer/hammer_26.jpg</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>stimuli/bread/bread_49.jpg</t>
-        </is>
-      </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
+          <t>dog</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>bread</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
           <t>house</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>hammer</t>
-        </is>
-      </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>bread</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -4691,16 +4691,16 @@
         <v>4</v>
       </c>
       <c r="T43" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="U43" t="n">
+        <v>5</v>
+      </c>
+      <c r="V43" t="n">
+        <v>3</v>
+      </c>
+      <c r="W43" t="n">
         <v>9</v>
-      </c>
-      <c r="V43" t="n">
-        <v>7</v>
-      </c>
-      <c r="W43" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="44">
@@ -4722,17 +4722,17 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>stimuli/house/house_05.jpg</t>
+          <t>stimuli/dog/dog_30.jpg</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_30.jpg</t>
+          <t>stimuli/hand/hand_30.jpg</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_30.jpg</t>
+          <t>stimuli/hammer/hammer_26.jpg</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -4742,17 +4742,17 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -4790,13 +4790,13 @@
         <v>5</v>
       </c>
       <c r="T44" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="U44" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="V44" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W44" t="n">
         <v>18</v>
@@ -4821,17 +4821,17 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_30.jpg</t>
+          <t>stimuli/hand/hand_30.jpg</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_16.jpg</t>
+          <t>stimuli/ball/ball_23.jpg</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_23.jpg</t>
+          <t>stimuli/bicycle/bicycle_35.jpg</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -4841,17 +4841,17 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -4889,13 +4889,13 @@
         <v>6</v>
       </c>
       <c r="T45" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="U45" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="V45" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W45" t="n">
         <v>15</v>
@@ -4920,42 +4920,42 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_16.jpg</t>
+          <t>stimuli/ball/ball_23.jpg</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_23.jpg</t>
+          <t>stimuli/bicycle/bicycle_35.jpg</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_22.jpg</t>
+          <t>stimuli/jacket/jacket_35.jpg</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_49.jpg</t>
+          <t>stimuli/house/house_05.jpg</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>house</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -4988,16 +4988,16 @@
         <v>7</v>
       </c>
       <c r="T46" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V46" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="W46" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="47">
@@ -5019,12 +5019,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_23.jpg</t>
+          <t>stimuli/bicycle/bicycle_35.jpg</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_22.jpg</t>
+          <t>stimuli/jacket/jacket_35.jpg</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -5039,12 +5039,12 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -5087,10 +5087,10 @@
         <v>8</v>
       </c>
       <c r="T47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U47" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="V47" t="n">
         <v>15</v>
@@ -5118,12 +5118,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_22.jpg</t>
+          <t>stimuli/jacket/jacket_35.jpg</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_26.jpg</t>
+          <t>stimuli/bread/bread_49.jpg</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -5133,17 +5133,17 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>stimuli/house/house_05.jpg</t>
+          <t>stimuli/dog/dog_30.jpg</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -5153,7 +5153,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -5186,16 +5186,16 @@
         <v>9</v>
       </c>
       <c r="T48" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="U48" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="V48" t="n">
         <v>17</v>
       </c>
       <c r="W48" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="49">
@@ -5217,42 +5217,42 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
+          <t>stimuli/bread/bread_49.jpg</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>stimuli/chair/chair_16.jpg</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
           <t>stimuli/hammer/hammer_26.jpg</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>stimuli/jacket/jacket_35.jpg</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
+      <c r="H49" t="inlineStr">
         <is>
           <t>stimuli/hand/hand_30.jpg</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>stimuli/dog/dog_30.jpg</t>
-        </is>
-      </c>
       <c r="I49" t="inlineStr">
         <is>
+          <t>bread</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>chair</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
           <t>hammer</t>
         </is>
       </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>jacket</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
+      <c r="L49" t="inlineStr">
         <is>
           <t>hand</t>
-        </is>
-      </c>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>dog</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -5285,16 +5285,16 @@
         <v>10</v>
       </c>
       <c r="T49" t="n">
+        <v>3</v>
+      </c>
+      <c r="U49" t="n">
+        <v>4</v>
+      </c>
+      <c r="V49" t="n">
         <v>7</v>
       </c>
-      <c r="U49" t="n">
-        <v>10</v>
-      </c>
-      <c r="V49" t="n">
+      <c r="W49" t="n">
         <v>8</v>
-      </c>
-      <c r="W49" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="50">
@@ -5316,12 +5316,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_35.jpg</t>
+          <t>stimuli/chair/chair_16.jpg</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_30.jpg</t>
+          <t>stimuli/hammer/hammer_26.jpg</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -5331,17 +5331,17 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_16.jpg</t>
+          <t>stimuli/ball/ball_23.jpg</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -5351,7 +5351,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -5384,16 +5384,16 @@
         <v>11</v>
       </c>
       <c r="T50" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="U50" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V50" t="n">
         <v>17</v>
       </c>
       <c r="W50" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -5415,42 +5415,42 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_30.jpg</t>
+          <t>stimuli/hammer/hammer_26.jpg</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_49.jpg</t>
+          <t>stimuli/house/house_05.jpg</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_35.jpg</t>
+          <t>stimuli/flower/flower_22.jpg</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_22.jpg</t>
+          <t>stimuli/jacket/jacket_35.jpg</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>house</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -5483,16 +5483,16 @@
         <v>12</v>
       </c>
       <c r="T51" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U51" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="V51" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="W51" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="52">
@@ -5514,7 +5514,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_49.jpg</t>
+          <t>stimuli/house/house_05.jpg</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -5524,17 +5524,17 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>stimuli/house/house_05.jpg</t>
+          <t>stimuli/dog/dog_30.jpg</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_35.jpg</t>
+          <t>stimuli/chair/chair_16.jpg</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>house</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -5544,12 +5544,12 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -5582,16 +5582,16 @@
         <v>13</v>
       </c>
       <c r="T52" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="U52" t="n">
         <v>15</v>
       </c>
       <c r="V52" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="W52" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="53">
@@ -5628,7 +5628,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_30.jpg</t>
+          <t>stimuli/hand/hand_30.jpg</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -5648,7 +5648,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -5690,7 +5690,7 @@
         <v>14</v>
       </c>
       <c r="W53" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="54">
@@ -5722,7 +5722,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_06.jpg</t>
+          <t>stimuli/chair/chair_04.jpg</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -5742,7 +5742,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -5786,7 +5786,7 @@
         <v>11</v>
       </c>
       <c r="V54" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="W54" t="n">
         <v>17</v>
@@ -5816,12 +5816,12 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_11.jpg</t>
+          <t>stimuli/hand/hand_20.jpg</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_28.jpg</t>
+          <t>stimuli/flower/flower_21.jpg</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -5836,12 +5836,12 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -5882,10 +5882,10 @@
         <v>11</v>
       </c>
       <c r="U55" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="V55" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="W55" t="n">
         <v>16</v>
@@ -5910,42 +5910,42 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_11.jpg</t>
+          <t>stimuli/hand/hand_20.jpg</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
+          <t>stimuli/house/house_10.jpg</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>stimuli/jacket/jacket_06.jpg</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
           <t>stimuli/bread/bread_25.jpg</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>stimuli/flower/flower_21.jpg</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>stimuli/hammer/hammer_09.jpg</t>
-        </is>
-      </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
+          <t>house</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>jacket</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
           <t>bread</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>flower</t>
-        </is>
-      </c>
-      <c r="L56" t="inlineStr">
-        <is>
-          <t>hammer</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -5978,16 +5978,16 @@
         <v>4</v>
       </c>
       <c r="T56" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="U56" t="n">
+        <v>9</v>
+      </c>
+      <c r="V56" t="n">
+        <v>10</v>
+      </c>
+      <c r="W56" t="n">
         <v>3</v>
-      </c>
-      <c r="V56" t="n">
-        <v>6</v>
-      </c>
-      <c r="W56" t="n">
-        <v>7</v>
       </c>
     </row>
     <row r="57">
@@ -6009,17 +6009,17 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_25.jpg</t>
+          <t>stimuli/house/house_10.jpg</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_06.jpg</t>
+          <t>stimuli/chair/chair_04.jpg</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_20.jpg</t>
+          <t>stimuli/hammer/hammer_09.jpg</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -6029,17 +6029,17 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>house</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -6077,13 +6077,13 @@
         <v>5</v>
       </c>
       <c r="T57" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="U57" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="V57" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W57" t="n">
         <v>17</v>
@@ -6108,17 +6108,17 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
+          <t>stimuli/chair/chair_04.jpg</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
           <t>stimuli/jacket/jacket_06.jpg</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>stimuli/flower/flower_21.jpg</t>
-        </is>
-      </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_04.jpg</t>
+          <t>stimuli/ball/ball_04.jpg</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -6128,17 +6128,17 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
+          <t>chair</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
           <t>jacket</t>
         </is>
       </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>flower</t>
-        </is>
-      </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -6176,13 +6176,13 @@
         <v>6</v>
       </c>
       <c r="T58" t="n">
+        <v>4</v>
+      </c>
+      <c r="U58" t="n">
         <v>10</v>
       </c>
-      <c r="U58" t="n">
-        <v>6</v>
-      </c>
       <c r="V58" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="W58" t="n">
         <v>16</v>
@@ -6207,17 +6207,17 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_21.jpg</t>
+          <t>stimuli/jacket/jacket_06.jpg</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_04.jpg</t>
+          <t>stimuli/ball/ball_04.jpg</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_04.jpg</t>
+          <t>stimuli/bicycle/bicycle_28.jpg</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -6227,17 +6227,17 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -6275,13 +6275,13 @@
         <v>7</v>
       </c>
       <c r="T59" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="U59" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="V59" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W59" t="n">
         <v>17</v>
@@ -6306,42 +6306,42 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
+          <t>stimuli/ball/ball_04.jpg</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>stimuli/flower/flower_21.jpg</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>stimuli/hand/hand_20.jpg</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
           <t>stimuli/chair/chair_04.jpg</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>stimuli/bicycle/bicycle_28.jpg</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>stimuli/dog/dog_11.jpg</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>stimuli/jacket/jacket_06.jpg</t>
-        </is>
-      </c>
       <c r="I60" t="inlineStr">
         <is>
+          <t>ball</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>flower</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>hand</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
           <t>chair</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>bicycle</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>dog</t>
-        </is>
-      </c>
-      <c r="L60" t="inlineStr">
-        <is>
-          <t>jacket</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
@@ -6374,16 +6374,16 @@
         <v>8</v>
       </c>
       <c r="T60" t="n">
+        <v>1</v>
+      </c>
+      <c r="U60" t="n">
+        <v>6</v>
+      </c>
+      <c r="V60" t="n">
+        <v>8</v>
+      </c>
+      <c r="W60" t="n">
         <v>4</v>
-      </c>
-      <c r="U60" t="n">
-        <v>2</v>
-      </c>
-      <c r="V60" t="n">
-        <v>5</v>
-      </c>
-      <c r="W60" t="n">
-        <v>10</v>
       </c>
     </row>
     <row r="61">
@@ -6405,12 +6405,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_28.jpg</t>
+          <t>stimuli/flower/flower_21.jpg</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_20.jpg</t>
+          <t>stimuli/hammer/hammer_09.jpg</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -6420,17 +6420,17 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_21.jpg</t>
+          <t>stimuli/jacket/jacket_06.jpg</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -6440,7 +6440,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
@@ -6473,16 +6473,16 @@
         <v>9</v>
       </c>
       <c r="T61" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="U61" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V61" t="n">
         <v>14</v>
       </c>
       <c r="W61" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="62">
@@ -6504,17 +6504,17 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_20.jpg</t>
+          <t>stimuli/hammer/hammer_09.jpg</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_04.jpg</t>
+          <t>stimuli/bicycle/bicycle_28.jpg</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>stimuli/house/house_10.jpg</t>
+          <t>stimuli/dog/dog_11.jpg</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -6524,17 +6524,17 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -6572,13 +6572,13 @@
         <v>10</v>
       </c>
       <c r="T62" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U62" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V62" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="W62" t="n">
         <v>17</v>
@@ -6603,42 +6603,42 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_04.jpg</t>
+          <t>stimuli/bicycle/bicycle_28.jpg</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
+          <t>stimuli/dog/dog_11.jpg</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>stimuli/lamp/lamp_30.jpg</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
           <t>stimuli/house/house_10.jpg</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>stimuli/lamp/lamp_30.jpg</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>stimuli/bread/bread_25.jpg</t>
-        </is>
-      </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
+          <t>dog</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>lamp</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
           <t>house</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>lamp</t>
-        </is>
-      </c>
-      <c r="L63" t="inlineStr">
-        <is>
-          <t>bread</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
@@ -6671,16 +6671,16 @@
         <v>11</v>
       </c>
       <c r="T63" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U63" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="V63" t="n">
         <v>14</v>
       </c>
       <c r="W63" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="64">
@@ -6702,42 +6702,42 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>stimuli/house/house_10.jpg</t>
+          <t>stimuli/dog/dog_11.jpg</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
+          <t>stimuli/bread/bread_25.jpg</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>stimuli/car/car_04.jpg</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
           <t>stimuli/hammer/hammer_09.jpg</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>stimuli/car/car_04.jpg</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>stimuli/hand/hand_20.jpg</t>
-        </is>
-      </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
+          <t>bread</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>car</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
           <t>hammer</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>car</t>
-        </is>
-      </c>
-      <c r="L64" t="inlineStr">
-        <is>
-          <t>hand</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -6770,16 +6770,16 @@
         <v>12</v>
       </c>
       <c r="T64" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="U64" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="V64" t="n">
         <v>11</v>
       </c>
       <c r="W64" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="65">
@@ -6801,7 +6801,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_09.jpg</t>
+          <t>stimuli/bread/bread_25.jpg</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -6811,17 +6811,17 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_25.jpg</t>
+          <t>stimuli/house/house_10.jpg</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_28.jpg</t>
+          <t>stimuli/flower/flower_21.jpg</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>house</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -6869,16 +6869,16 @@
         <v>13</v>
       </c>
       <c r="T65" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="U65" t="n">
         <v>17</v>
       </c>
       <c r="V65" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="W65" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="66">
@@ -6910,7 +6910,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_21.jpg</t>
+          <t>stimuli/jacket/jacket_06.jpg</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -6930,7 +6930,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -6974,7 +6974,7 @@
         <v>16</v>
       </c>
       <c r="V66" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="W66" t="n">
         <v>14</v>
@@ -7009,7 +7009,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_23.jpg</t>
+          <t>stimuli/bicycle/bicycle_35.jpg</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -7029,7 +7029,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -7073,7 +7073,7 @@
         <v>14</v>
       </c>
       <c r="V67" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W67" t="n">
         <v>18</v>
@@ -7103,12 +7103,12 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_35.jpg</t>
+          <t>stimuli/flower/flower_22.jpg</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_30.jpg</t>
+          <t>stimuli/hand/hand_30.jpg</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -7123,12 +7123,12 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -7169,10 +7169,10 @@
         <v>14</v>
       </c>
       <c r="U68" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="V68" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="W68" t="n">
         <v>15</v>
@@ -7197,42 +7197,42 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_35.jpg</t>
+          <t>stimuli/flower/flower_22.jpg</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>stimuli/house/house_05.jpg</t>
+          <t>stimuli/dog/dog_30.jpg</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_22.jpg</t>
+          <t>stimuli/jacket/jacket_35.jpg</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_30.jpg</t>
+          <t>stimuli/hammer/hammer_26.jpg</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
@@ -7265,16 +7265,16 @@
         <v>4</v>
       </c>
       <c r="T69" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="U69" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="V69" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="W69" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="70">
@@ -7296,42 +7296,42 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
+          <t>stimuli/dog/dog_30.jpg</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>stimuli/hand/hand_30.jpg</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>stimuli/chair/chair_16.jpg</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
           <t>stimuli/house/house_05.jpg</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>stimuli/dog/dog_30.jpg</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>stimuli/jacket/jacket_35.jpg</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>stimuli/bread/bread_49.jpg</t>
-        </is>
-      </c>
       <c r="I70" t="inlineStr">
         <is>
+          <t>dog</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>hand</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>chair</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
           <t>house</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>dog</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>jacket</t>
-        </is>
-      </c>
-      <c r="L70" t="inlineStr">
-        <is>
-          <t>bread</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
@@ -7364,16 +7364,16 @@
         <v>5</v>
       </c>
       <c r="T70" t="n">
+        <v>5</v>
+      </c>
+      <c r="U70" t="n">
+        <v>8</v>
+      </c>
+      <c r="V70" t="n">
+        <v>4</v>
+      </c>
+      <c r="W70" t="n">
         <v>9</v>
-      </c>
-      <c r="U70" t="n">
-        <v>5</v>
-      </c>
-      <c r="V70" t="n">
-        <v>10</v>
-      </c>
-      <c r="W70" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="71">
@@ -7395,17 +7395,17 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_30.jpg</t>
+          <t>stimuli/hand/hand_30.jpg</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_16.jpg</t>
+          <t>stimuli/ball/ball_23.jpg</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_26.jpg</t>
+          <t>stimuli/bread/bread_49.jpg</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -7415,17 +7415,17 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -7463,13 +7463,13 @@
         <v>6</v>
       </c>
       <c r="T71" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="U71" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="V71" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="W71" t="n">
         <v>15</v>
@@ -7494,12 +7494,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_16.jpg</t>
+          <t>stimuli/ball/ball_23.jpg</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_23.jpg</t>
+          <t>stimuli/bicycle/bicycle_35.jpg</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -7509,17 +7509,17 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_35.jpg</t>
+          <t>stimuli/flower/flower_22.jpg</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -7529,7 +7529,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
@@ -7562,16 +7562,16 @@
         <v>7</v>
       </c>
       <c r="T72" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U72" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V72" t="n">
         <v>17</v>
       </c>
       <c r="W72" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="73">
@@ -7593,12 +7593,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_23.jpg</t>
+          <t>stimuli/bicycle/bicycle_35.jpg</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_22.jpg</t>
+          <t>stimuli/jacket/jacket_35.jpg</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -7608,17 +7608,17 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>stimuli/house/house_05.jpg</t>
+          <t>stimuli/dog/dog_30.jpg</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -7628,7 +7628,7 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
@@ -7661,16 +7661,16 @@
         <v>8</v>
       </c>
       <c r="T73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U73" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="V73" t="n">
         <v>18</v>
       </c>
       <c r="W73" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="74">
@@ -7692,17 +7692,17 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_22.jpg</t>
+          <t>stimuli/jacket/jacket_35.jpg</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_26.jpg</t>
+          <t>stimuli/bread/bread_49.jpg</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_49.jpg</t>
+          <t>stimuli/house/house_05.jpg</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -7712,17 +7712,17 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>house</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -7760,13 +7760,13 @@
         <v>9</v>
       </c>
       <c r="T74" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="U74" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="V74" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="W74" t="n">
         <v>14</v>
@@ -7791,12 +7791,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_26.jpg</t>
+          <t>stimuli/bread/bread_49.jpg</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_35.jpg</t>
+          <t>stimuli/chair/chair_16.jpg</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -7806,17 +7806,17 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_16.jpg</t>
+          <t>stimuli/ball/ball_23.jpg</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -7826,7 +7826,7 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
@@ -7859,16 +7859,16 @@
         <v>10</v>
       </c>
       <c r="T75" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="U75" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="V75" t="n">
         <v>14</v>
       </c>
       <c r="W75" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="76">
@@ -7890,17 +7890,17 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_35.jpg</t>
+          <t>stimuli/chair/chair_16.jpg</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_30.jpg</t>
+          <t>stimuli/hammer/hammer_26.jpg</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_49.jpg</t>
+          <t>stimuli/house/house_05.jpg</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -7910,17 +7910,17 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>house</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -7958,13 +7958,13 @@
         <v>11</v>
       </c>
       <c r="T76" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="U76" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V76" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="W76" t="n">
         <v>18</v>
@@ -7989,12 +7989,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_30.jpg</t>
+          <t>stimuli/hammer/hammer_26.jpg</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_49.jpg</t>
+          <t>stimuli/house/house_05.jpg</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -8004,17 +8004,17 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_22.jpg</t>
+          <t>stimuli/jacket/jacket_35.jpg</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>house</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -8024,7 +8024,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
@@ -8057,16 +8057,16 @@
         <v>12</v>
       </c>
       <c r="T77" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U77" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="V77" t="n">
         <v>17</v>
       </c>
       <c r="W77" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="78">
@@ -8088,7 +8088,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_49.jpg</t>
+          <t>stimuli/house/house_05.jpg</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -8103,12 +8103,12 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_23.jpg</t>
+          <t>stimuli/bicycle/bicycle_35.jpg</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>house</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -8123,7 +8123,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
@@ -8156,7 +8156,7 @@
         <v>13</v>
       </c>
       <c r="T78" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="U78" t="n">
         <v>15</v>
@@ -8165,7 +8165,7 @@
         <v>14</v>
       </c>
       <c r="W78" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="79">
@@ -8197,7 +8197,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_30.jpg</t>
+          <t>stimuli/hand/hand_30.jpg</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -8217,7 +8217,7 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -8261,7 +8261,7 @@
         <v>18</v>
       </c>
       <c r="V79" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="W79" t="n">
         <v>17</v>
@@ -8296,7 +8296,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_28.jpg</t>
+          <t>stimuli/flower/flower_21.jpg</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -8316,7 +8316,7 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -8360,7 +8360,7 @@
         <v>11</v>
       </c>
       <c r="V80" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="W80" t="n">
         <v>16</v>
@@ -8390,12 +8390,12 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_11.jpg</t>
+          <t>stimuli/hand/hand_20.jpg</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_20.jpg</t>
+          <t>stimuli/hammer/hammer_09.jpg</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -8410,12 +8410,12 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -8456,10 +8456,10 @@
         <v>11</v>
       </c>
       <c r="U81" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="V81" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W81" t="n">
         <v>17</v>
@@ -8484,19 +8484,19 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
+          <t>stimuli/hand/hand_20.jpg</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>stimuli/house/house_10.jpg</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
           <t>stimuli/dog/dog_11.jpg</t>
         </is>
       </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>stimuli/bread/bread_25.jpg</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>stimuli/house/house_10.jpg</t>
-        </is>
-      </c>
       <c r="H82" t="inlineStr">
         <is>
           <t>stimuli/pencil/pencil_15.jpg</t>
@@ -8504,17 +8504,17 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
+          <t>hand</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>house</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
           <t>dog</t>
-        </is>
-      </c>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>bread</t>
-        </is>
-      </c>
-      <c r="K82" t="inlineStr">
-        <is>
-          <t>house</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -8552,13 +8552,13 @@
         <v>4</v>
       </c>
       <c r="T82" t="n">
+        <v>8</v>
+      </c>
+      <c r="U82" t="n">
+        <v>9</v>
+      </c>
+      <c r="V82" t="n">
         <v>5</v>
-      </c>
-      <c r="U82" t="n">
-        <v>3</v>
-      </c>
-      <c r="V82" t="n">
-        <v>9</v>
       </c>
       <c r="W82" t="n">
         <v>16</v>
@@ -8583,42 +8583,42 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
+          <t>stimuli/house/house_10.jpg</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>stimuli/chair/chair_04.jpg</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>stimuli/ball/ball_04.jpg</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
           <t>stimuli/bread/bread_25.jpg</t>
         </is>
       </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>stimuli/jacket/jacket_06.jpg</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>stimuli/chair/chair_04.jpg</t>
-        </is>
-      </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>stimuli/hammer/hammer_09.jpg</t>
-        </is>
-      </c>
       <c r="I83" t="inlineStr">
         <is>
+          <t>house</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>chair</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>ball</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
           <t>bread</t>
-        </is>
-      </c>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t>jacket</t>
-        </is>
-      </c>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t>chair</t>
-        </is>
-      </c>
-      <c r="L83" t="inlineStr">
-        <is>
-          <t>hammer</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
@@ -8651,16 +8651,16 @@
         <v>5</v>
       </c>
       <c r="T83" t="n">
+        <v>9</v>
+      </c>
+      <c r="U83" t="n">
+        <v>4</v>
+      </c>
+      <c r="V83" t="n">
+        <v>1</v>
+      </c>
+      <c r="W83" t="n">
         <v>3</v>
-      </c>
-      <c r="U83" t="n">
-        <v>10</v>
-      </c>
-      <c r="V83" t="n">
-        <v>4</v>
-      </c>
-      <c r="W83" t="n">
-        <v>7</v>
       </c>
     </row>
     <row r="84">
@@ -8682,14 +8682,14 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
+          <t>stimuli/chair/chair_04.jpg</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
           <t>stimuli/jacket/jacket_06.jpg</t>
         </is>
       </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>stimuli/flower/flower_21.jpg</t>
-        </is>
-      </c>
       <c r="G84" t="inlineStr">
         <is>
           <t>stimuli/lamp/lamp_30.jpg</t>
@@ -8697,19 +8697,19 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_11.jpg</t>
+          <t>stimuli/hand/hand_20.jpg</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
+          <t>chair</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
           <t>jacket</t>
         </is>
       </c>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t>flower</t>
-        </is>
-      </c>
       <c r="K84" t="inlineStr">
         <is>
           <t>lamp</t>
@@ -8717,7 +8717,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
@@ -8750,16 +8750,16 @@
         <v>6</v>
       </c>
       <c r="T84" t="n">
+        <v>4</v>
+      </c>
+      <c r="U84" t="n">
         <v>10</v>
-      </c>
-      <c r="U84" t="n">
-        <v>6</v>
       </c>
       <c r="V84" t="n">
         <v>14</v>
       </c>
       <c r="W84" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="85">
@@ -8781,17 +8781,17 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_21.jpg</t>
+          <t>stimuli/jacket/jacket_06.jpg</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_04.jpg</t>
+          <t>stimuli/ball/ball_04.jpg</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_04.jpg</t>
+          <t>stimuli/bicycle/bicycle_28.jpg</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -8801,17 +8801,17 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -8849,13 +8849,13 @@
         <v>7</v>
       </c>
       <c r="T85" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="U85" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="V85" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W85" t="n">
         <v>17</v>
@@ -8880,17 +8880,17 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_04.jpg</t>
+          <t>stimuli/ball/ball_04.jpg</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_28.jpg</t>
+          <t>stimuli/flower/flower_21.jpg</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_09.jpg</t>
+          <t>stimuli/bread/bread_25.jpg</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -8900,17 +8900,17 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -8948,13 +8948,13 @@
         <v>8</v>
       </c>
       <c r="T86" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U86" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="V86" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="W86" t="n">
         <v>11</v>
@@ -8979,42 +8979,42 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_28.jpg</t>
+          <t>stimuli/flower/flower_21.jpg</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_20.jpg</t>
+          <t>stimuli/hammer/hammer_09.jpg</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>stimuli/house/house_10.jpg</t>
+          <t>stimuli/dog/dog_11.jpg</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_06.jpg</t>
+          <t>stimuli/chair/chair_04.jpg</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
@@ -9047,16 +9047,16 @@
         <v>9</v>
       </c>
       <c r="T87" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="U87" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V87" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="W87" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="88">
@@ -9078,42 +9078,42 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
+          <t>stimuli/hammer/hammer_09.jpg</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>stimuli/bicycle/bicycle_28.jpg</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
           <t>stimuli/hand/hand_20.jpg</t>
         </is>
       </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>stimuli/ball/ball_04.jpg</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>stimuli/dog/dog_11.jpg</t>
-        </is>
-      </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_21.jpg</t>
+          <t>stimuli/jacket/jacket_06.jpg</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
+          <t>hammer</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
           <t>hand</t>
         </is>
       </c>
-      <c r="J88" t="inlineStr">
-        <is>
-          <t>ball</t>
-        </is>
-      </c>
-      <c r="K88" t="inlineStr">
-        <is>
-          <t>dog</t>
-        </is>
-      </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
@@ -9146,16 +9146,16 @@
         <v>10</v>
       </c>
       <c r="T88" t="n">
+        <v>7</v>
+      </c>
+      <c r="U88" t="n">
+        <v>2</v>
+      </c>
+      <c r="V88" t="n">
         <v>8</v>
       </c>
-      <c r="U88" t="n">
-        <v>1</v>
-      </c>
-      <c r="V88" t="n">
-        <v>5</v>
-      </c>
       <c r="W88" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="89">
@@ -9177,42 +9177,42 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_04.jpg</t>
+          <t>stimuli/bicycle/bicycle_28.jpg</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
+          <t>stimuli/dog/dog_11.jpg</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>stimuli/car/car_04.jpg</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
           <t>stimuli/house/house_10.jpg</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>stimuli/car/car_04.jpg</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>stimuli/bread/bread_25.jpg</t>
-        </is>
-      </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
+          <t>dog</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>car</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
           <t>house</t>
-        </is>
-      </c>
-      <c r="K89" t="inlineStr">
-        <is>
-          <t>car</t>
-        </is>
-      </c>
-      <c r="L89" t="inlineStr">
-        <is>
-          <t>bread</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
@@ -9245,16 +9245,16 @@
         <v>11</v>
       </c>
       <c r="T89" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U89" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="V89" t="n">
         <v>11</v>
       </c>
       <c r="W89" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="90">
@@ -9276,12 +9276,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>stimuli/house/house_10.jpg</t>
+          <t>stimuli/dog/dog_11.jpg</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_09.jpg</t>
+          <t>stimuli/bread/bread_25.jpg</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -9291,17 +9291,17 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_06.jpg</t>
+          <t>stimuli/chair/chair_04.jpg</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -9311,7 +9311,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
@@ -9344,16 +9344,16 @@
         <v>12</v>
       </c>
       <c r="T90" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="U90" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="V90" t="n">
         <v>14</v>
       </c>
       <c r="W90" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="91">
@@ -9375,7 +9375,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_09.jpg</t>
+          <t>stimuli/bread/bread_25.jpg</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -9385,17 +9385,17 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_25.jpg</t>
+          <t>stimuli/house/house_10.jpg</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_04.jpg</t>
+          <t>stimuli/ball/ball_04.jpg</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -9405,12 +9405,12 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>house</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
@@ -9443,16 +9443,16 @@
         <v>13</v>
       </c>
       <c r="T91" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="U91" t="n">
         <v>17</v>
       </c>
       <c r="V91" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="W91" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="92">
@@ -9489,7 +9489,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_04.jpg</t>
+          <t>stimuli/bicycle/bicycle_28.jpg</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -9509,7 +9509,7 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
@@ -9551,7 +9551,7 @@
         <v>11</v>
       </c>
       <c r="W92" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="93">
@@ -9583,7 +9583,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_16.jpg</t>
+          <t>stimuli/ball/ball_23.jpg</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -9603,7 +9603,7 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -9647,7 +9647,7 @@
         <v>14</v>
       </c>
       <c r="V93" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="W93" t="n">
         <v>18</v>
@@ -9677,19 +9677,19 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_35.jpg</t>
+          <t>stimuli/flower/flower_22.jpg</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
+          <t>stimuli/dog/dog_30.jpg</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
           <t>stimuli/house/house_05.jpg</t>
         </is>
       </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>stimuli/bread/bread_49.jpg</t>
-        </is>
-      </c>
       <c r="I94" t="inlineStr">
         <is>
           <t>lamp</t>
@@ -9697,17 +9697,17 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
+          <t>dog</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
           <t>house</t>
-        </is>
-      </c>
-      <c r="L94" t="inlineStr">
-        <is>
-          <t>bread</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
@@ -9743,13 +9743,13 @@
         <v>14</v>
       </c>
       <c r="U94" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="V94" t="n">
+        <v>5</v>
+      </c>
+      <c r="W94" t="n">
         <v>9</v>
-      </c>
-      <c r="W94" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="95">
@@ -9771,17 +9771,17 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_35.jpg</t>
+          <t>stimuli/flower/flower_22.jpg</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>stimuli/house/house_05.jpg</t>
+          <t>stimuli/dog/dog_30.jpg</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_26.jpg</t>
+          <t>stimuli/bread/bread_49.jpg</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -9791,17 +9791,17 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
@@ -9839,13 +9839,13 @@
         <v>4</v>
       </c>
       <c r="T95" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="U95" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="V95" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="W95" t="n">
         <v>18</v>
@@ -9870,17 +9870,17 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>stimuli/house/house_05.jpg</t>
+          <t>stimuli/dog/dog_30.jpg</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_30.jpg</t>
+          <t>stimuli/hand/hand_30.jpg</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_22.jpg</t>
+          <t>stimuli/jacket/jacket_35.jpg</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -9890,17 +9890,17 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
@@ -9938,13 +9938,13 @@
         <v>5</v>
       </c>
       <c r="T96" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="U96" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="V96" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="W96" t="n">
         <v>15</v>
@@ -9969,17 +9969,17 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_30.jpg</t>
+          <t>stimuli/hand/hand_30.jpg</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_16.jpg</t>
+          <t>stimuli/ball/ball_23.jpg</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_30.jpg</t>
+          <t>stimuli/hammer/hammer_26.jpg</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -9989,17 +9989,17 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
@@ -10037,13 +10037,13 @@
         <v>6</v>
       </c>
       <c r="T97" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="U97" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="V97" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W97" t="n">
         <v>18</v>
@@ -10068,19 +10068,19 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
+          <t>stimuli/ball/ball_23.jpg</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>stimuli/bicycle/bicycle_35.jpg</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
           <t>stimuli/chair/chair_16.jpg</t>
         </is>
       </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>stimuli/ball/ball_23.jpg</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>stimuli/jacket/jacket_35.jpg</t>
-        </is>
-      </c>
       <c r="H98" t="inlineStr">
         <is>
           <t>stimuli/key/key_10.jpg</t>
@@ -10088,17 +10088,17 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
+          <t>ball</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
           <t>chair</t>
-        </is>
-      </c>
-      <c r="J98" t="inlineStr">
-        <is>
-          <t>ball</t>
-        </is>
-      </c>
-      <c r="K98" t="inlineStr">
-        <is>
-          <t>jacket</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
@@ -10136,13 +10136,13 @@
         <v>7</v>
       </c>
       <c r="T98" t="n">
+        <v>1</v>
+      </c>
+      <c r="U98" t="n">
+        <v>2</v>
+      </c>
+      <c r="V98" t="n">
         <v>4</v>
-      </c>
-      <c r="U98" t="n">
-        <v>1</v>
-      </c>
-      <c r="V98" t="n">
-        <v>10</v>
       </c>
       <c r="W98" t="n">
         <v>15</v>
@@ -10167,42 +10167,42 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_23.jpg</t>
+          <t>stimuli/bicycle/bicycle_35.jpg</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
+          <t>stimuli/jacket/jacket_35.jpg</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
           <t>stimuli/flower/flower_22.jpg</t>
         </is>
       </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>stimuli/bicycle/bicycle_35.jpg</t>
-        </is>
-      </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_30.jpg</t>
+          <t>stimuli/hand/hand_30.jpg</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
+          <t>jacket</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
           <t>flower</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr">
-        <is>
-          <t>bicycle</t>
-        </is>
-      </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
@@ -10235,16 +10235,16 @@
         <v>8</v>
       </c>
       <c r="T99" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U99" t="n">
+        <v>10</v>
+      </c>
+      <c r="V99" t="n">
         <v>6</v>
       </c>
-      <c r="V99" t="n">
-        <v>2</v>
-      </c>
       <c r="W99" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="100">
@@ -10266,12 +10266,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_22.jpg</t>
+          <t>stimuli/jacket/jacket_35.jpg</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_26.jpg</t>
+          <t>stimuli/bread/bread_49.jpg</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -10281,17 +10281,17 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_16.jpg</t>
+          <t>stimuli/ball/ball_23.jpg</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
@@ -10301,7 +10301,7 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
@@ -10334,16 +10334,16 @@
         <v>9</v>
       </c>
       <c r="T100" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="U100" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="V100" t="n">
         <v>17</v>
       </c>
       <c r="W100" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="101">
@@ -10365,12 +10365,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_26.jpg</t>
+          <t>stimuli/bread/bread_49.jpg</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_35.jpg</t>
+          <t>stimuli/chair/chair_16.jpg</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -10380,17 +10380,17 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_23.jpg</t>
+          <t>stimuli/bicycle/bicycle_35.jpg</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
@@ -10400,7 +10400,7 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
@@ -10433,16 +10433,16 @@
         <v>10</v>
       </c>
       <c r="T101" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="U101" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="V101" t="n">
         <v>14</v>
       </c>
       <c r="W101" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="102">
@@ -10464,42 +10464,42 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_35.jpg</t>
+          <t>stimuli/chair/chair_16.jpg</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_30.jpg</t>
+          <t>stimuli/hammer/hammer_26.jpg</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>stimuli/house/house_05.jpg</t>
+          <t>stimuli/dog/dog_30.jpg</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_16.jpg</t>
+          <t>stimuli/ball/ball_23.jpg</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
@@ -10532,16 +10532,16 @@
         <v>11</v>
       </c>
       <c r="T102" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="U102" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V102" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="W102" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="103">
@@ -10563,12 +10563,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_30.jpg</t>
+          <t>stimuli/hammer/hammer_26.jpg</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_49.jpg</t>
+          <t>stimuli/house/house_05.jpg</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -10578,17 +10578,17 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>stimuli/house/house_05.jpg</t>
+          <t>stimuli/dog/dog_30.jpg</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>house</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
@@ -10598,7 +10598,7 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
@@ -10631,16 +10631,16 @@
         <v>12</v>
       </c>
       <c r="T103" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U103" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="V103" t="n">
         <v>17</v>
       </c>
       <c r="W103" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="104">
@@ -10662,7 +10662,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_49.jpg</t>
+          <t>stimuli/house/house_05.jpg</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -10672,17 +10672,17 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_35.jpg</t>
+          <t>stimuli/flower/flower_22.jpg</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_30.jpg</t>
+          <t>stimuli/hand/hand_30.jpg</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>house</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -10692,12 +10692,12 @@
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
@@ -10730,16 +10730,16 @@
         <v>13</v>
       </c>
       <c r="T104" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="U104" t="n">
         <v>15</v>
       </c>
       <c r="V104" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="W104" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="105">
@@ -10776,7 +10776,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_22.jpg</t>
+          <t>stimuli/jacket/jacket_35.jpg</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -10796,7 +10796,7 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
@@ -10838,7 +10838,7 @@
         <v>14</v>
       </c>
       <c r="W105" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
